--- a/lang.compare.xlsx
+++ b/lang.compare.xlsx
@@ -74,19 +74,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>2.74470610472921e-06</v>
+        <v>3.87821087088902e-06</v>
       </c>
       <c r="C2">
-        <v>0.000157445037725016</v>
+        <v>0.0001505990185251</v>
       </c>
       <c r="D2">
-        <v>7.93252672467914e-05</v>
+        <v>7.24792480468751e-05</v>
       </c>
       <c r="E2">
-        <v>0.000106573104858398</v>
+        <v>0.000113419124058315</v>
       </c>
       <c r="F2">
-        <v>-0.000157445037725016</v>
+        <v>-0.0001505990185251</v>
       </c>
       <c r="G2">
         <v>-7.81197704782244e-05</v>
@@ -95,7 +95,7 @@
         <v>0.000264018142583414</v>
       </c>
       <c r="I2">
-        <v>-7.93252672467914e-05</v>
+        <v>-7.24792480468751e-05</v>
       </c>
       <c r="J2">
         <v>7.81197704782244e-05</v>
@@ -111,19 +111,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>2.08273507329437e-08</v>
+        <v>0.819443099233151</v>
       </c>
       <c r="C3">
-        <v>-0.00158128706711328</v>
+        <v>1.43764035393738e-06</v>
       </c>
       <c r="D3">
-        <v>-0.00165299006870815</v>
+        <v>-7.02653612409322e-05</v>
       </c>
       <c r="E3">
-        <v>0.00197928292410714</v>
+        <v>0.000396558216639928</v>
       </c>
       <c r="F3">
-        <v>0.00158128706711328</v>
+        <v>-1.43764035393738e-06</v>
       </c>
       <c r="G3">
         <v>-7.17030015948696e-05</v>
@@ -132,7 +132,7 @@
         <v>0.000397995856993865</v>
       </c>
       <c r="I3">
-        <v>0.00165299006870815</v>
+        <v>7.02653612409322e-05</v>
       </c>
       <c r="J3">
         <v>7.17030015948696e-05</v>
@@ -148,19 +148,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.000517946020100579</v>
+        <v>0.00181238974913112</v>
       </c>
       <c r="C4">
-        <v>0.000156729064786175</v>
+        <v>0.000129685585956655</v>
       </c>
       <c r="D4">
-        <v>1.21593475341795e-05</v>
+        <v>-1.48841312953404e-05</v>
       </c>
       <c r="E4">
-        <v>0.000180278505597796</v>
+        <v>0.000207321984427316</v>
       </c>
       <c r="F4">
-        <v>-0.000156729064786175</v>
+        <v>-0.000129685585956655</v>
       </c>
       <c r="G4">
         <v>-0.000144569717251995</v>
@@ -169,7 +169,7 @@
         <v>0.00033700757038397</v>
       </c>
       <c r="I4">
-        <v>-1.21593475341795e-05</v>
+        <v>1.48841312953404e-05</v>
       </c>
       <c r="J4">
         <v>0.000144569717251995</v>
@@ -185,19 +185,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>3.63139969150605e-05</v>
+        <v>0.000272825863196768</v>
       </c>
       <c r="C5">
-        <v>0.000126131723975829</v>
+        <v>0.000100893414388078</v>
       </c>
       <c r="D5">
-        <v>1.91756657191685e-05</v>
+        <v>-6.06264386858254e-06</v>
       </c>
       <c r="E5">
-        <v>0.000176974705287388</v>
+        <v>0.000202213014875139</v>
       </c>
       <c r="F5">
-        <v>-0.000126131723975829</v>
+        <v>-0.000100893414388078</v>
       </c>
       <c r="G5">
         <v>-0.000106956058256661</v>
@@ -206,7 +206,7 @@
         <v>0.000303106429263218</v>
       </c>
       <c r="I5">
-        <v>-1.91756657191685e-05</v>
+        <v>6.06264386858254e-06</v>
       </c>
       <c r="J5">
         <v>0.000106956058256661</v>
@@ -222,19 +222,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>7.79914130610848e-07</v>
+        <v>1.77722144423242e-06</v>
       </c>
       <c r="C6">
-        <v>0.000137633565567999</v>
+        <v>0.00011951375355628</v>
       </c>
       <c r="D6">
-        <v>2.81333923339845e-05</v>
+        <v>1.00135803222654e-05</v>
       </c>
       <c r="E6">
-        <v>0.000124011720929827</v>
+        <v>0.000142131532941546</v>
       </c>
       <c r="F6">
-        <v>-0.000137633565567999</v>
+        <v>-0.00011951375355628</v>
       </c>
       <c r="G6">
         <v>-0.000109500173234015</v>
@@ -243,7 +243,7 @@
         <v>0.000261645286497826</v>
       </c>
       <c r="I6">
-        <v>-2.81333923339845e-05</v>
+        <v>-1.00135803222654e-05</v>
       </c>
       <c r="J6">
         <v>0.000109500173234015</v>
@@ -259,19 +259,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>7.0791270745385e-07</v>
+        <v>1.09246928370332e-06</v>
       </c>
       <c r="C7">
-        <v>0.00010975116726643</v>
+        <v>9.67743846039023e-05</v>
       </c>
       <c r="D7">
-        <v>1.41348157610212e-05</v>
+        <v>1.15803309849339e-06</v>
       </c>
       <c r="E7">
-        <v>0.000130585261753627</v>
+        <v>0.000143562044416155</v>
       </c>
       <c r="F7">
-        <v>-0.00010975116726643</v>
+        <v>-9.67743846039023e-05</v>
       </c>
       <c r="G7">
         <v>-9.56163515054089e-05</v>
@@ -280,7 +280,7 @@
         <v>0.000240336429020057</v>
       </c>
       <c r="I7">
-        <v>-1.41348157610212e-05</v>
+        <v>-1.15803309849339e-06</v>
       </c>
       <c r="J7">
         <v>9.56163515054089e-05</v>
@@ -296,19 +296,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>7.28950727113542e-07</v>
+        <v>2.54653950815253e-07</v>
       </c>
       <c r="C8">
-        <v>-0.00112013103301121</v>
+        <v>-0.00126941512332581</v>
       </c>
       <c r="D8">
-        <v>-0.00113926615033831</v>
+        <v>-0.0012885502406529</v>
       </c>
       <c r="E8">
-        <v>0.00179699489048549</v>
+        <v>0.00194627898080008</v>
       </c>
       <c r="F8">
-        <v>0.00112013103301121</v>
+        <v>0.00126941512332581</v>
       </c>
       <c r="G8">
         <v>-1.91351173270965e-05</v>
@@ -317,7 +317,7 @@
         <v>0.000676863857474278</v>
       </c>
       <c r="I8">
-        <v>0.00113926615033831</v>
+        <v>0.0012885502406529</v>
       </c>
       <c r="J8">
         <v>1.91351173270965e-05</v>
@@ -333,19 +333,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.0106364440002353</v>
+        <v>0.00958849120382088</v>
       </c>
       <c r="C9">
-        <v>8.02352936131816e-05</v>
+        <v>9.32461360727237e-05</v>
       </c>
       <c r="D9">
-        <v>-0.000166927065168109</v>
+        <v>-0.000153916222708566</v>
       </c>
       <c r="E9">
-        <v>0.000481298991612025</v>
+        <v>0.000468288149152483</v>
       </c>
       <c r="F9">
-        <v>-8.02352936131816e-05</v>
+        <v>-9.32461360727237e-05</v>
       </c>
       <c r="G9">
         <v>-0.00024716235878129</v>
@@ -354,7 +354,7 @@
         <v>0.000561534285225207</v>
       </c>
       <c r="I9">
-        <v>0.000166927065168109</v>
+        <v>0.000153916222708566</v>
       </c>
       <c r="J9">
         <v>0.00024716235878129</v>
@@ -370,19 +370,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.53044625831322e-05</v>
+        <v>1.41446033696813e-06</v>
       </c>
       <c r="C10">
-        <v>-0.000112551819516479</v>
+        <v>-0.000127333771420776</v>
       </c>
       <c r="D10">
-        <v>-0.000263588769095284</v>
+        <v>-0.000278370720999581</v>
       </c>
       <c r="E10">
-        <v>0.000532627105712891</v>
+        <v>0.000547409057617187</v>
       </c>
       <c r="F10">
-        <v>0.000112551819516479</v>
+        <v>0.000127333771420776</v>
       </c>
       <c r="G10">
         <v>-0.000151036949578805</v>
@@ -391,7 +391,7 @@
         <v>0.000420075286196412</v>
       </c>
       <c r="I10">
-        <v>0.000263588769095284</v>
+        <v>0.000278370720999581</v>
       </c>
       <c r="J10">
         <v>0.000151036949578805</v>
@@ -407,19 +407,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>8.54804951266885e-08</v>
+        <v>8.59630733263117e-09</v>
       </c>
       <c r="C11">
-        <v>-0.000123782268409351</v>
+        <v>-0.000125314959275004</v>
       </c>
       <c r="D11">
-        <v>-2.40462166922433e-05</v>
+        <v>-2.55789075578961e-05</v>
       </c>
       <c r="E11">
-        <v>0.000159638268607003</v>
+        <v>0.000161170959472656</v>
       </c>
       <c r="F11">
-        <v>0.000123782268409351</v>
+        <v>0.000125314959275004</v>
       </c>
       <c r="G11">
         <v>9.97360517171078e-05</v>
@@ -428,7 +428,7 @@
         <v>3.58560001976522e-05</v>
       </c>
       <c r="I11">
-        <v>2.40462166922433e-05</v>
+        <v>2.55789075578961e-05</v>
       </c>
       <c r="J11">
         <v>-9.97360517171078e-05</v>
@@ -444,19 +444,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>4.45505047297345e-08</v>
+        <v>2.77440471707635e-08</v>
       </c>
       <c r="C12">
-        <v>-0.000103808798095477</v>
+        <v>-0.000112085328770003</v>
       </c>
       <c r="D12">
-        <v>-1.10353742327008e-05</v>
+        <v>-1.93119049072267e-05</v>
       </c>
       <c r="E12">
-        <v>0.000127553939819336</v>
+        <v>0.000135830470493862</v>
       </c>
       <c r="F12">
-        <v>0.000103808798095477</v>
+        <v>0.000112085328770003</v>
       </c>
       <c r="G12">
         <v>9.27734238627766e-05</v>
@@ -465,7 +465,7 @@
         <v>2.37451417238585e-05</v>
       </c>
       <c r="I12">
-        <v>1.10353742327008e-05</v>
+        <v>1.93119049072267e-05</v>
       </c>
       <c r="J12">
         <v>-9.27734238627766e-05</v>
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>2.94921223198408e-06</v>
+        <v>2.28701351423499e-06</v>
       </c>
       <c r="C13">
-        <v>-0.00235668604831777</v>
+        <v>-0.00253836100559316</v>
       </c>
       <c r="D13">
-        <v>-0.00359211649213518</v>
+        <v>-0.00377379144941057</v>
       </c>
       <c r="E13">
-        <v>0.00518574033464704</v>
+        <v>0.00536741529192243</v>
       </c>
       <c r="F13">
-        <v>0.00235668604831777</v>
+        <v>0.00253836100559316</v>
       </c>
       <c r="G13">
         <v>-0.00123543044381742</v>
@@ -502,7 +502,7 @@
         <v>0.00282905428632928</v>
       </c>
       <c r="I13">
-        <v>0.00359211649213518</v>
+        <v>0.00377379144941057</v>
       </c>
       <c r="J13">
         <v>0.00123543044381742</v>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>4.77728967496205e-13</v>
+        <v>4.2765790908561e-13</v>
       </c>
       <c r="C14">
-        <v>-0.00389312765556887</v>
+        <v>-0.00399844054793773</v>
       </c>
       <c r="D14">
-        <v>0.00446724891662595</v>
+        <v>0.00436193602425709</v>
       </c>
       <c r="E14">
-        <v>0.00746965408325195</v>
+        <v>0.00757496697562081</v>
       </c>
       <c r="F14">
-        <v>0.00389312765556887</v>
+        <v>0.00399844054793773</v>
       </c>
       <c r="G14">
         <v>0.00836037657219481</v>
@@ -539,7 +539,7 @@
         <v>0.00357652642768309</v>
       </c>
       <c r="I14">
-        <v>-0.00446724891662595</v>
+        <v>-0.00436193602425709</v>
       </c>
       <c r="J14">
         <v>-0.00836037657219481</v>
@@ -555,19 +555,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>9.74480385274035e-10</v>
+        <v>8.95056251337678e-11</v>
       </c>
       <c r="C15">
-        <v>-0.0101350002862871</v>
+        <v>-0.0108087371310311</v>
       </c>
       <c r="D15">
-        <v>-0.0149615492139544</v>
+        <v>-0.0156352860586984</v>
       </c>
       <c r="E15">
-        <v>0.0162365777151925</v>
+        <v>0.0169103145599365</v>
       </c>
       <c r="F15">
-        <v>0.0101350002862871</v>
+        <v>0.0108087371310311</v>
       </c>
       <c r="G15">
         <v>-0.00482654892766732</v>
@@ -576,7 +576,7 @@
         <v>0.00610157742890546</v>
       </c>
       <c r="I15">
-        <v>0.0149615492139544</v>
+        <v>0.0156352860586984</v>
       </c>
       <c r="J15">
         <v>0.00482654892766732</v>
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.21929841778723e-08</v>
+        <v>4.37108660888974e-06</v>
       </c>
       <c r="C16">
-        <v>-0.000763176494988979</v>
+        <v>-0.000825437803931499</v>
       </c>
       <c r="D16">
-        <v>-0.000811917441231864</v>
+        <v>-0.000874178750174384</v>
       </c>
       <c r="E16">
-        <v>0.00142124720982143</v>
+        <v>0.00148350851876395</v>
       </c>
       <c r="F16">
-        <v>0.000763176494988979</v>
+        <v>0.000825437803931499</v>
       </c>
       <c r="G16">
         <v>-4.87409462428857e-05</v>
@@ -613,7 +613,7 @@
         <v>0.00065807071483245</v>
       </c>
       <c r="I16">
-        <v>0.000811917441231864</v>
+        <v>0.000874178750174384</v>
       </c>
       <c r="J16">
         <v>4.87409462428857e-05</v>
@@ -629,19 +629,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.263725550153175</v>
+        <v>0.518883039694389</v>
       </c>
       <c r="C17">
-        <v>-2.43557473627983e-05</v>
+        <v>-3.86949219059067e-05</v>
       </c>
       <c r="D17">
-        <v>6.40324183872774e-06</v>
+        <v>-7.93593270438056e-06</v>
       </c>
       <c r="E17">
-        <v>0.000253404889787946</v>
+        <v>0.000267744064331055</v>
       </c>
       <c r="F17">
-        <v>2.43557473627983e-05</v>
+        <v>3.86949219059067e-05</v>
       </c>
       <c r="G17">
         <v>3.07589892015261e-05</v>
@@ -650,7 +650,7 @@
         <v>0.000229049142425148</v>
       </c>
       <c r="I17">
-        <v>-6.40324183872774e-06</v>
+        <v>7.93593270438056e-06</v>
       </c>
       <c r="J17">
         <v>-3.07589892015261e-05</v>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>4.49495995979987e-10</v>
+        <v>1.10983444656654e-11</v>
       </c>
       <c r="C18">
-        <v>-0.00229637955739495</v>
+        <v>-0.0022701875734908</v>
       </c>
       <c r="D18">
-        <v>-0.00167570795331682</v>
+        <v>-0.00164951596941267</v>
       </c>
       <c r="E18">
-        <v>0.0031698431287493</v>
+        <v>0.00314365114484515</v>
       </c>
       <c r="F18">
-        <v>0.00229637955739495</v>
+        <v>0.0022701875734908</v>
       </c>
       <c r="G18">
         <v>0.00062067160407813</v>
@@ -687,7 +687,7 @@
         <v>0.000873463571354348</v>
       </c>
       <c r="I18">
-        <v>0.00167570795331682</v>
+        <v>0.00164951596941267</v>
       </c>
       <c r="J18">
         <v>-0.00062067160407813</v>
@@ -703,19 +703,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>4.44774772567769e-10</v>
+        <v>2.9339186635724e-10</v>
       </c>
       <c r="C19">
-        <v>0.0007365474702965</v>
+        <v>0.000738216400350211</v>
       </c>
       <c r="D19">
-        <v>0.00144144466945103</v>
+        <v>0.00144311359950474</v>
       </c>
       <c r="E19">
-        <v>0.000140258244105748</v>
+        <v>0.000138589314052037</v>
       </c>
       <c r="F19">
-        <v>-0.0007365474702965</v>
+        <v>-0.000738216400350211</v>
       </c>
       <c r="G19">
         <v>0.000704897199154532</v>
@@ -724,7 +724,7 @@
         <v>0.000876805714402248</v>
       </c>
       <c r="I19">
-        <v>-0.00144144466945103</v>
+        <v>-0.00144311359950474</v>
       </c>
       <c r="J19">
         <v>-0.000704897199154532</v>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>2.43814601841308e-09</v>
+        <v>1.30535515729946e-09</v>
       </c>
       <c r="C20">
-        <v>0.000588332751379182</v>
+        <v>0.000574708832573378</v>
       </c>
       <c r="D20">
-        <v>0.000918660845075334</v>
+        <v>0.00090503692626953</v>
       </c>
       <c r="E20">
-        <v>0.00016157967703683</v>
+        <v>0.000175203595842634</v>
       </c>
       <c r="F20">
-        <v>-0.000588332751379182</v>
+        <v>-0.000574708832573378</v>
       </c>
       <c r="G20">
         <v>0.000330328093696152</v>
@@ -761,7 +761,7 @@
         <v>0.000749912428416012</v>
       </c>
       <c r="I20">
-        <v>-0.000918660845075334</v>
+        <v>-0.00090503692626953</v>
       </c>
       <c r="J20">
         <v>-0.000330328093696152</v>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>2.07276775743281e-08</v>
+        <v>2.80839811406253e-08</v>
       </c>
       <c r="C21">
-        <v>0.000528763915748901</v>
+        <v>0.000516298030041591</v>
       </c>
       <c r="D21">
-        <v>0.000780718667166573</v>
+        <v>0.000768252781459263</v>
       </c>
       <c r="E21">
-        <v>0.000175237655639649</v>
+        <v>0.000187703541346959</v>
       </c>
       <c r="F21">
-        <v>-0.000528763915748901</v>
+        <v>-0.000516298030041591</v>
       </c>
       <c r="G21">
         <v>0.000251954751417673</v>
@@ -798,7 +798,7 @@
         <v>0.000704001571388549</v>
       </c>
       <c r="I21">
-        <v>-0.000780718667166573</v>
+        <v>-0.000768252781459263</v>
       </c>
       <c r="J21">
         <v>-0.000251954751417673</v>
@@ -814,19 +814,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>5.51623191569206e-11</v>
+        <v>3.86991549916615e-11</v>
       </c>
       <c r="C22">
-        <v>-0.00850368647817439</v>
+        <v>-0.00882115784614664</v>
       </c>
       <c r="D22">
-        <v>-0.00876692363194057</v>
+        <v>-0.00908439499991282</v>
       </c>
       <c r="E22">
-        <v>0.00946157319205147</v>
+        <v>0.00977904456002373</v>
       </c>
       <c r="F22">
-        <v>0.00850368647817439</v>
+        <v>0.00882115784614664</v>
       </c>
       <c r="G22">
         <v>-0.000263237153766178</v>
@@ -835,7 +835,7 @@
         <v>0.000957886713877087</v>
       </c>
       <c r="I22">
-        <v>0.00876692363194057</v>
+        <v>0.00908439499991282</v>
       </c>
       <c r="J22">
         <v>0.000263237153766178</v>
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>2.80238744432282e-08</v>
+        <v>4.62348825891468e-10</v>
       </c>
       <c r="C23">
-        <v>-0.00913964033783746</v>
+        <v>-0.00930772543610406</v>
       </c>
       <c r="D23">
-        <v>-0.00710402216230119</v>
+        <v>-0.0072721072605678</v>
       </c>
       <c r="E23">
-        <v>0.00945465905325753</v>
+        <v>0.00962274415152413</v>
       </c>
       <c r="F23">
-        <v>0.00913964033783746</v>
+        <v>0.00930772543610406</v>
       </c>
       <c r="G23">
         <v>0.00203561817553626</v>
@@ -872,7 +872,7 @@
         <v>0.000315018715420073</v>
       </c>
       <c r="I23">
-        <v>0.00710402216230119</v>
+        <v>0.0072721072605678</v>
       </c>
       <c r="J23">
         <v>-0.00203561817553626</v>
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.81178766434087e-08</v>
+        <v>6.80875256175995e-09</v>
       </c>
       <c r="C24">
-        <v>-0.0136215689287513</v>
+        <v>-0.0144235068494579</v>
       </c>
       <c r="D24">
-        <v>-0.0151292255946568</v>
+        <v>-0.0159311635153634</v>
       </c>
       <c r="E24">
-        <v>0.0159100805010114</v>
+        <v>0.0167120184217181</v>
       </c>
       <c r="F24">
-        <v>0.0136215689287513</v>
+        <v>0.0144235068494579</v>
       </c>
       <c r="G24">
         <v>-0.00150765666590554</v>
@@ -909,7 +909,7 @@
         <v>0.00228851157226018</v>
       </c>
       <c r="I24">
-        <v>0.0151292255946568</v>
+        <v>0.0159311635153634</v>
       </c>
       <c r="J24">
         <v>0.00150765666590554</v>
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>2.36366741843685e-05</v>
+        <v>7.97397259333366e-10</v>
       </c>
       <c r="C25">
-        <v>-0.000381493577151561</v>
+        <v>-0.000740279478902396</v>
       </c>
       <c r="D25">
-        <v>0.00201940536499023</v>
+        <v>0.0016606194632394</v>
       </c>
       <c r="E25">
-        <v>0.00140469414847238</v>
+        <v>0.00176348005022321</v>
       </c>
       <c r="F25">
-        <v>0.000381493577151561</v>
+        <v>0.000740279478902396</v>
       </c>
       <c r="G25">
         <v>0.00240089894214179</v>
@@ -946,7 +946,7 @@
         <v>0.00102320057132082</v>
       </c>
       <c r="I25">
-        <v>-0.00201940536499023</v>
+        <v>-0.0016606194632394</v>
       </c>
       <c r="J25">
         <v>-0.00240089894214179</v>
@@ -962,19 +962,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>4.00560695723584e-11</v>
+        <v>1.0680345496894e-13</v>
       </c>
       <c r="C26">
-        <v>-0.00730463120791163</v>
+        <v>-0.00750234832958085</v>
       </c>
       <c r="D26">
-        <v>-0.00678181648254394</v>
+        <v>-0.00697953360421317</v>
       </c>
       <c r="E26">
-        <v>0.00776420320783342</v>
+        <v>0.00796192032950265</v>
       </c>
       <c r="F26">
-        <v>0.00730463120791163</v>
+        <v>0.00750234832958085</v>
       </c>
       <c r="G26">
         <v>0.000522814725367685</v>
@@ -983,7 +983,7 @@
         <v>0.000459571999921796</v>
       </c>
       <c r="I26">
-        <v>0.00678181648254394</v>
+        <v>0.00697953360421317</v>
       </c>
       <c r="J26">
         <v>-0.000522814725367685</v>
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>5.60720521125546e-08</v>
+        <v>1.84297473948547e-08</v>
       </c>
       <c r="C27">
-        <v>-0.0142123815982943</v>
+        <v>-0.0137640184303954</v>
       </c>
       <c r="D27">
-        <v>-0.0125953810555594</v>
+        <v>-0.0121470178876605</v>
       </c>
       <c r="E27">
-        <v>0.0168675354548863</v>
+        <v>0.0164191722869873</v>
       </c>
       <c r="F27">
-        <v>0.0142123815982943</v>
+        <v>0.0137640184303954</v>
       </c>
       <c r="G27">
         <v>0.00161700054273492</v>
@@ -1020,7 +1020,7 @@
         <v>0.00265515385659195</v>
       </c>
       <c r="I27">
-        <v>0.0125953810555594</v>
+        <v>0.0121470178876605</v>
       </c>
       <c r="J27">
         <v>-0.00161700054273492</v>
@@ -1036,19 +1036,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.000204069469053492</v>
+        <v>0.00417047903254708</v>
       </c>
       <c r="C28">
-        <v>0.000360344689397607</v>
+        <v>0.000234766217805113</v>
       </c>
       <c r="D28">
-        <v>9.08715384347095e-05</v>
+        <v>-3.47069331577849e-05</v>
       </c>
       <c r="E28">
-        <v>0.000537463596888951</v>
+        <v>0.000663042068481445</v>
       </c>
       <c r="F28">
-        <v>-0.000360344689397607</v>
+        <v>-0.000234766217805113</v>
       </c>
       <c r="G28">
         <v>-0.000269473150962897</v>
@@ -1057,7 +1057,7 @@
         <v>0.000897808286286558</v>
       </c>
       <c r="I28">
-        <v>-9.08715384347095e-05</v>
+        <v>3.47069331577849e-05</v>
       </c>
       <c r="J28">
         <v>0.000269473150962897</v>
@@ -1073,19 +1073,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>4.14513379298764e-06</v>
+        <v>6.38050767776122e-07</v>
       </c>
       <c r="C29">
-        <v>-0.0115837598449226</v>
+        <v>-0.00991980252157579</v>
       </c>
       <c r="D29">
-        <v>-0.0100164754050119</v>
+        <v>-0.00835251808166502</v>
       </c>
       <c r="E29">
-        <v>0.0163581371307373</v>
+        <v>0.0146941798073905</v>
       </c>
       <c r="F29">
-        <v>0.0115837598449226</v>
+        <v>0.00991980252157579</v>
       </c>
       <c r="G29">
         <v>0.00156728443991077</v>
@@ -1094,7 +1094,7 @@
         <v>0.00477437728581468</v>
       </c>
       <c r="I29">
-        <v>0.0100164754050119</v>
+        <v>0.00835251808166502</v>
       </c>
       <c r="J29">
         <v>-0.00156728443991077</v>
@@ -1113,16 +1113,16 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0.0243259981803671</v>
+        <v>0.0235695300886748</v>
       </c>
       <c r="D30">
-        <v>-0.00993333544049943</v>
+        <v>-0.0106898035321917</v>
       </c>
       <c r="E30">
-        <v>0.0119738238198416</v>
+        <v>0.0127302919115339</v>
       </c>
       <c r="F30">
-        <v>-0.0243259981803671</v>
+        <v>-0.0235695300886748</v>
       </c>
       <c r="G30">
         <v>-0.0342593336208665</v>
@@ -1131,7 +1131,7 @@
         <v>0.0362998220002087</v>
       </c>
       <c r="I30">
-        <v>0.00993333544049943</v>
+        <v>0.0106898035321917</v>
       </c>
       <c r="J30">
         <v>0.0342593336208665</v>
@@ -1147,19 +1147,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>3.71815900885863e-05</v>
+        <v>8.94061105286559e-05</v>
       </c>
       <c r="C31">
-        <v>-0.00694028859860347</v>
+        <v>-0.00588160792800149</v>
       </c>
       <c r="D31">
-        <v>-0.00919028690883091</v>
+        <v>-0.00813160623822893</v>
       </c>
       <c r="E31">
-        <v>0.0165797301701137</v>
+        <v>0.0155210494995117</v>
       </c>
       <c r="F31">
-        <v>0.00694028859860347</v>
+        <v>0.00588160792800149</v>
       </c>
       <c r="G31">
         <v>-0.00224999831022744</v>
@@ -1168,7 +1168,7 @@
         <v>0.00963944157151023</v>
       </c>
       <c r="I31">
-        <v>0.00919028690883091</v>
+        <v>0.00813160623822893</v>
       </c>
       <c r="J31">
         <v>0.00224999831022744</v>
@@ -1184,19 +1184,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>2.8709572164054e-08</v>
+        <v>2.18244893746e-06</v>
       </c>
       <c r="C32">
-        <v>-0.00407207411938413</v>
+        <v>-0.00381076735668882</v>
       </c>
       <c r="D32">
-        <v>-0.00259365354265485</v>
+        <v>-0.00233234677995954</v>
       </c>
       <c r="E32">
-        <v>0.00651243754795619</v>
+        <v>0.00625113078526088</v>
       </c>
       <c r="F32">
-        <v>0.00407207411938413</v>
+        <v>0.00381076735668882</v>
       </c>
       <c r="G32">
         <v>0.00147842057672928</v>
@@ -1205,7 +1205,7 @@
         <v>0.00244036342857206</v>
       </c>
       <c r="I32">
-        <v>0.00259365354265485</v>
+        <v>0.00233234677995954</v>
       </c>
       <c r="J32">
         <v>-0.00147842057672928</v>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>3.99673611983786e-07</v>
+        <v>1.00862142227154e-06</v>
       </c>
       <c r="C33">
-        <v>-0.00185010132138684</v>
+        <v>-0.00170790166885126</v>
       </c>
       <c r="D33">
-        <v>-0.00233939715794155</v>
+        <v>-0.00219719750540597</v>
       </c>
       <c r="E33">
-        <v>0.00410066332135882</v>
+        <v>0.00395846366882324</v>
       </c>
       <c r="F33">
-        <v>0.00185010132138684</v>
+        <v>0.00170790166885126</v>
       </c>
       <c r="G33">
         <v>-0.000489295836554707</v>
@@ -1242,7 +1242,7 @@
         <v>0.00225056199997198</v>
       </c>
       <c r="I33">
-        <v>0.00233939715794155</v>
+        <v>0.00219719750540597</v>
       </c>
       <c r="J33">
         <v>0.000489295836554707</v>

--- a/lang.compare.xlsx
+++ b/lang.compare.xlsx
@@ -74,19 +74,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>3.87821087088902e-06</v>
+        <v>2.8880773738412e-06</v>
       </c>
       <c r="C2">
-        <v>0.0001505990185251</v>
+        <v>0.000161838751539887</v>
       </c>
       <c r="D2">
-        <v>7.24792480468751e-05</v>
+        <v>8.37189810616629e-05</v>
       </c>
       <c r="E2">
-        <v>0.000113419124058315</v>
+        <v>0.000102179391043527</v>
       </c>
       <c r="F2">
-        <v>-0.0001505990185251</v>
+        <v>-0.000161838751539887</v>
       </c>
       <c r="G2">
         <v>-7.81197704782244e-05</v>
@@ -95,7 +95,7 @@
         <v>0.000264018142583414</v>
       </c>
       <c r="I2">
-        <v>-7.24792480468751e-05</v>
+        <v>-8.37189810616629e-05</v>
       </c>
       <c r="J2">
         <v>7.81197704782244e-05</v>
@@ -111,19 +111,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.819443099233151</v>
+        <v>0.133146839472534</v>
       </c>
       <c r="C3">
-        <v>1.43764035393738e-06</v>
+        <v>4.20369183952321e-05</v>
       </c>
       <c r="D3">
-        <v>-7.02653612409322e-05</v>
+        <v>-2.96660831996375e-05</v>
       </c>
       <c r="E3">
-        <v>0.000396558216639928</v>
+        <v>0.000355958938598633</v>
       </c>
       <c r="F3">
-        <v>-1.43764035393738e-06</v>
+        <v>-4.20369183952321e-05</v>
       </c>
       <c r="G3">
         <v>-7.17030015948696e-05</v>
@@ -132,7 +132,7 @@
         <v>0.000397995856993865</v>
       </c>
       <c r="I3">
-        <v>7.02653612409322e-05</v>
+        <v>2.96660831996375e-05</v>
       </c>
       <c r="J3">
         <v>7.17030015948696e-05</v>
@@ -148,19 +148,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.00181238974913112</v>
+        <v>0.000908219851103137</v>
       </c>
       <c r="C4">
-        <v>0.000129685585956655</v>
+        <v>0.000143990700702748</v>
       </c>
       <c r="D4">
-        <v>-1.48841312953404e-05</v>
+        <v>-5.79016549246601e-07</v>
       </c>
       <c r="E4">
-        <v>0.000207321984427316</v>
+        <v>0.000193016869681222</v>
       </c>
       <c r="F4">
-        <v>-0.000129685585956655</v>
+        <v>-0.000143990700702748</v>
       </c>
       <c r="G4">
         <v>-0.000144569717251995</v>
@@ -169,7 +169,7 @@
         <v>0.00033700757038397</v>
       </c>
       <c r="I4">
-        <v>1.48841312953404e-05</v>
+        <v>5.79016549246601e-07</v>
       </c>
       <c r="J4">
         <v>0.000144569717251995</v>
@@ -185,19 +185,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.000272825863196768</v>
+        <v>5.14921587447615e-05</v>
       </c>
       <c r="C5">
-        <v>0.000100893414388078</v>
+        <v>0.000118229851068463</v>
       </c>
       <c r="D5">
-        <v>-6.06264386858254e-06</v>
+        <v>1.12737928118025e-05</v>
       </c>
       <c r="E5">
-        <v>0.000202213014875139</v>
+        <v>0.000184876578194754</v>
       </c>
       <c r="F5">
-        <v>-0.000100893414388078</v>
+        <v>-0.000118229851068463</v>
       </c>
       <c r="G5">
         <v>-0.000106956058256661</v>
@@ -206,7 +206,7 @@
         <v>0.000303106429263218</v>
       </c>
       <c r="I5">
-        <v>6.06264386858254e-06</v>
+        <v>-1.12737928118025e-05</v>
       </c>
       <c r="J5">
         <v>0.000106956058256661</v>
@@ -222,19 +222,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.77722144423242e-06</v>
+        <v>1.07732810112514e-06</v>
       </c>
       <c r="C6">
-        <v>0.00011951375355628</v>
+        <v>0.000135010961197882</v>
       </c>
       <c r="D6">
-        <v>1.00135803222654e-05</v>
+        <v>2.5510787963867e-05</v>
       </c>
       <c r="E6">
-        <v>0.000142131532941546</v>
+        <v>0.000126634325299944</v>
       </c>
       <c r="F6">
-        <v>-0.00011951375355628</v>
+        <v>-0.000135010961197882</v>
       </c>
       <c r="G6">
         <v>-0.000109500173234015</v>
@@ -243,7 +243,7 @@
         <v>0.000261645286497826</v>
       </c>
       <c r="I6">
-        <v>-1.00135803222654e-05</v>
+        <v>-2.5510787963867e-05</v>
       </c>
       <c r="J6">
         <v>0.000109500173234015</v>
@@ -259,19 +259,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>1.09246928370332e-06</v>
+        <v>6.45277429127434e-07</v>
       </c>
       <c r="C7">
-        <v>9.67743846039023e-05</v>
+        <v>0.000109921466251503</v>
       </c>
       <c r="D7">
-        <v>1.15803309849339e-06</v>
+        <v>1.43051147460937e-05</v>
       </c>
       <c r="E7">
-        <v>0.000143562044416155</v>
+        <v>0.000130414962768555</v>
       </c>
       <c r="F7">
-        <v>-9.67743846039023e-05</v>
+        <v>-0.000109921466251503</v>
       </c>
       <c r="G7">
         <v>-9.56163515054089e-05</v>
@@ -280,7 +280,7 @@
         <v>0.000240336429020057</v>
       </c>
       <c r="I7">
-        <v>-1.15803309849339e-06</v>
+        <v>-1.43051147460937e-05</v>
       </c>
       <c r="J7">
         <v>9.56163515054089e-05</v>
@@ -296,19 +296,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>2.54653950815253e-07</v>
+        <v>1.11607514619256e-06</v>
       </c>
       <c r="C8">
-        <v>-0.00126941512332581</v>
+        <v>-0.00112564872012756</v>
       </c>
       <c r="D8">
-        <v>-0.0012885502406529</v>
+        <v>-0.00114478383745466</v>
       </c>
       <c r="E8">
-        <v>0.00194627898080008</v>
+        <v>0.00180251257760184</v>
       </c>
       <c r="F8">
-        <v>0.00126941512332581</v>
+        <v>0.00112564872012756</v>
       </c>
       <c r="G8">
         <v>-1.91351173270965e-05</v>
@@ -317,7 +317,7 @@
         <v>0.000676863857474278</v>
       </c>
       <c r="I8">
-        <v>0.0012885502406529</v>
+        <v>0.00114478383745466</v>
       </c>
       <c r="J8">
         <v>1.91351173270965e-05</v>
@@ -333,19 +333,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.00958849120382088</v>
+        <v>0.00195854527598812</v>
       </c>
       <c r="C9">
-        <v>9.32461360727237e-05</v>
+        <v>0.000107210652848673</v>
       </c>
       <c r="D9">
-        <v>-0.000153916222708566</v>
+        <v>-0.000139951705932618</v>
       </c>
       <c r="E9">
-        <v>0.000468288149152483</v>
+        <v>0.000454323632376534</v>
       </c>
       <c r="F9">
-        <v>-9.32461360727237e-05</v>
+        <v>-0.000107210652848673</v>
       </c>
       <c r="G9">
         <v>-0.00024716235878129</v>
@@ -354,7 +354,7 @@
         <v>0.000561534285225207</v>
       </c>
       <c r="I9">
-        <v>0.000153916222708566</v>
+        <v>0.000139951705932618</v>
       </c>
       <c r="J9">
         <v>0.00024716235878129</v>
@@ -370,19 +370,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.41446033696813e-06</v>
+        <v>0.000107178562171379</v>
       </c>
       <c r="C10">
-        <v>-0.000127333771420776</v>
+        <v>-9.4091409534615e-05</v>
       </c>
       <c r="D10">
-        <v>-0.000278370720999581</v>
+        <v>-0.00024512835911342</v>
       </c>
       <c r="E10">
-        <v>0.000547409057617187</v>
+        <v>0.000514166695731027</v>
       </c>
       <c r="F10">
-        <v>0.000127333771420776</v>
+        <v>9.4091409534615e-05</v>
       </c>
       <c r="G10">
         <v>-0.000151036949578805</v>
@@ -391,7 +391,7 @@
         <v>0.000420075286196412</v>
       </c>
       <c r="I10">
-        <v>0.000278370720999581</v>
+        <v>0.00024512835911342</v>
       </c>
       <c r="J10">
         <v>0.000151036949578805</v>
@@ -407,19 +407,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>8.59630733263117e-09</v>
+        <v>3.52053190532094e-09</v>
       </c>
       <c r="C11">
-        <v>-0.000125314959275004</v>
+        <v>-0.000126609231561555</v>
       </c>
       <c r="D11">
-        <v>-2.55789075578961e-05</v>
+        <v>-2.68731798444475e-05</v>
       </c>
       <c r="E11">
-        <v>0.000161170959472656</v>
+        <v>0.000162465231759208</v>
       </c>
       <c r="F11">
-        <v>0.000125314959275004</v>
+        <v>0.000126609231561555</v>
       </c>
       <c r="G11">
         <v>9.97360517171078e-05</v>
@@ -428,7 +428,7 @@
         <v>3.58560001976522e-05</v>
       </c>
       <c r="I11">
-        <v>2.55789075578961e-05</v>
+        <v>2.68731798444475e-05</v>
       </c>
       <c r="J11">
         <v>-9.97360517171078e-05</v>
@@ -444,19 +444,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>2.77440471707635e-08</v>
+        <v>6.01729571975434e-09</v>
       </c>
       <c r="C12">
-        <v>-0.000112085328770003</v>
+        <v>-0.000101152133928346</v>
       </c>
       <c r="D12">
-        <v>-1.93119049072267e-05</v>
+        <v>-8.37871006556911e-06</v>
       </c>
       <c r="E12">
-        <v>0.000135830470493862</v>
+        <v>0.000124897275652204</v>
       </c>
       <c r="F12">
-        <v>0.000112085328770003</v>
+        <v>0.000101152133928346</v>
       </c>
       <c r="G12">
         <v>9.27734238627766e-05</v>
@@ -465,7 +465,7 @@
         <v>2.37451417238585e-05</v>
       </c>
       <c r="I12">
-        <v>1.93119049072267e-05</v>
+        <v>8.37871006556911e-06</v>
       </c>
       <c r="J12">
         <v>-9.27734238627766e-05</v>
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>2.28701351423499e-06</v>
+        <v>3.05110607619447e-07</v>
       </c>
       <c r="C13">
-        <v>-0.00253836100559316</v>
+        <v>-0.00252167170505605</v>
       </c>
       <c r="D13">
-        <v>-0.00377379144941057</v>
+        <v>-0.00375710214887346</v>
       </c>
       <c r="E13">
-        <v>0.00536741529192243</v>
+        <v>0.00535072599138532</v>
       </c>
       <c r="F13">
-        <v>0.00253836100559316</v>
+        <v>0.00252167170505605</v>
       </c>
       <c r="G13">
         <v>-0.00123543044381742</v>
@@ -502,7 +502,7 @@
         <v>0.00282905428632928</v>
       </c>
       <c r="I13">
-        <v>0.00377379144941057</v>
+        <v>0.00375710214887346</v>
       </c>
       <c r="J13">
         <v>0.00123543044381742</v>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>4.2765790908561e-13</v>
+        <v>2.32319725135296e-12</v>
       </c>
       <c r="C14">
-        <v>-0.00399844054793773</v>
+        <v>-0.00398948282132291</v>
       </c>
       <c r="D14">
-        <v>0.00436193602425709</v>
+        <v>0.0043708937508719</v>
       </c>
       <c r="E14">
-        <v>0.00757496697562081</v>
+        <v>0.007566009249006</v>
       </c>
       <c r="F14">
-        <v>0.00399844054793773</v>
+        <v>0.00398948282132291</v>
       </c>
       <c r="G14">
         <v>0.00836037657219481</v>
@@ -539,7 +539,7 @@
         <v>0.00357652642768309</v>
       </c>
       <c r="I14">
-        <v>-0.00436193602425709</v>
+        <v>-0.0043708937508719</v>
       </c>
       <c r="J14">
         <v>-0.00836037657219481</v>
@@ -555,19 +555,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>8.95056251337678e-11</v>
+        <v>4.65343068519643e-09</v>
       </c>
       <c r="C15">
-        <v>-0.0108087371310311</v>
+        <v>-0.0099132710077226</v>
       </c>
       <c r="D15">
-        <v>-0.0156352860586984</v>
+        <v>-0.0147398199353899</v>
       </c>
       <c r="E15">
-        <v>0.0169103145599365</v>
+        <v>0.0160148484366281</v>
       </c>
       <c r="F15">
-        <v>0.0108087371310311</v>
+        <v>0.0099132710077226</v>
       </c>
       <c r="G15">
         <v>-0.00482654892766732</v>
@@ -576,7 +576,7 @@
         <v>0.00610157742890546</v>
       </c>
       <c r="I15">
-        <v>0.0156352860586984</v>
+        <v>0.0147398199353899</v>
       </c>
       <c r="J15">
         <v>0.00482654892766732</v>
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>4.37108660888974e-06</v>
+        <v>6.23875917135205e-05</v>
       </c>
       <c r="C16">
-        <v>-0.000825437803931499</v>
+        <v>-0.000677243627121373</v>
       </c>
       <c r="D16">
-        <v>-0.000874178750174384</v>
+        <v>-0.000725984573364259</v>
       </c>
       <c r="E16">
-        <v>0.00148350851876395</v>
+        <v>0.00133531434195382</v>
       </c>
       <c r="F16">
-        <v>0.000825437803931499</v>
+        <v>0.000677243627121373</v>
       </c>
       <c r="G16">
         <v>-4.87409462428857e-05</v>
@@ -613,7 +613,7 @@
         <v>0.00065807071483245</v>
       </c>
       <c r="I16">
-        <v>0.000874178750174384</v>
+        <v>0.000725984573364259</v>
       </c>
       <c r="J16">
         <v>4.87409462428857e-05</v>
@@ -629,19 +629,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.518883039694389</v>
+        <v>0.255692927982255</v>
       </c>
       <c r="C17">
-        <v>-3.86949219059067e-05</v>
+        <v>-4.92193991833897e-05</v>
       </c>
       <c r="D17">
-        <v>-7.93593270438056e-06</v>
+        <v>-1.84604099818637e-05</v>
       </c>
       <c r="E17">
-        <v>0.000267744064331055</v>
+        <v>0.000278268541608538</v>
       </c>
       <c r="F17">
-        <v>3.86949219059067e-05</v>
+        <v>4.92193991833897e-05</v>
       </c>
       <c r="G17">
         <v>3.07589892015261e-05</v>
@@ -650,7 +650,7 @@
         <v>0.000229049142425148</v>
       </c>
       <c r="I17">
-        <v>7.93593270438056e-06</v>
+        <v>1.84604099818637e-05</v>
       </c>
       <c r="J17">
         <v>-3.07589892015261e-05</v>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.10983444656654e-11</v>
+        <v>4.99280739001676e-10</v>
       </c>
       <c r="C18">
-        <v>-0.0022701875734908</v>
+        <v>-0.00240758479464733</v>
       </c>
       <c r="D18">
-        <v>-0.00164951596941267</v>
+        <v>-0.0017869131905692</v>
       </c>
       <c r="E18">
-        <v>0.00314365114484515</v>
+        <v>0.00328104836600167</v>
       </c>
       <c r="F18">
-        <v>0.0022701875734908</v>
+        <v>0.00240758479464733</v>
       </c>
       <c r="G18">
         <v>0.00062067160407813</v>
@@ -687,7 +687,7 @@
         <v>0.000873463571354348</v>
       </c>
       <c r="I18">
-        <v>0.00164951596941267</v>
+        <v>0.0017869131905692</v>
       </c>
       <c r="J18">
         <v>-0.00062067160407813</v>
@@ -703,19 +703,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>2.9339186635724e-10</v>
+        <v>1.53631059709857e-10</v>
       </c>
       <c r="C19">
-        <v>0.000738216400350211</v>
+        <v>0.000742848532744185</v>
       </c>
       <c r="D19">
-        <v>0.00144311359950474</v>
+        <v>0.00144774573189872</v>
       </c>
       <c r="E19">
-        <v>0.000138589314052037</v>
+        <v>0.000133957181658063</v>
       </c>
       <c r="F19">
-        <v>-0.000738216400350211</v>
+        <v>-0.000742848532744185</v>
       </c>
       <c r="G19">
         <v>0.000704897199154532</v>
@@ -724,7 +724,7 @@
         <v>0.000876805714402248</v>
       </c>
       <c r="I19">
-        <v>-0.00144311359950474</v>
+        <v>-0.00144774573189872</v>
       </c>
       <c r="J19">
         <v>-0.000704897199154532</v>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.30535515729946e-09</v>
+        <v>1.35604234407254e-09</v>
       </c>
       <c r="C20">
-        <v>0.000574708832573378</v>
+        <v>0.000596541162459679</v>
       </c>
       <c r="D20">
-        <v>0.00090503692626953</v>
+        <v>0.00092686925615583</v>
       </c>
       <c r="E20">
-        <v>0.000175203595842634</v>
+        <v>0.000153371265956334</v>
       </c>
       <c r="F20">
-        <v>-0.000574708832573378</v>
+        <v>-0.000596541162459679</v>
       </c>
       <c r="G20">
         <v>0.000330328093696152</v>
@@ -761,7 +761,7 @@
         <v>0.000749912428416012</v>
       </c>
       <c r="I20">
-        <v>-0.00090503692626953</v>
+        <v>-0.00092686925615583</v>
       </c>
       <c r="J20">
         <v>-0.000330328093696152</v>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>2.80839811406253e-08</v>
+        <v>1.69214147340278e-08</v>
       </c>
       <c r="C21">
-        <v>0.000516298030041591</v>
+        <v>0.000532238015044381</v>
       </c>
       <c r="D21">
-        <v>0.000768252781459263</v>
+        <v>0.000784192766462053</v>
       </c>
       <c r="E21">
-        <v>0.000187703541346959</v>
+        <v>0.000171763556344169</v>
       </c>
       <c r="F21">
-        <v>-0.000516298030041591</v>
+        <v>-0.000532238015044381</v>
       </c>
       <c r="G21">
         <v>0.000251954751417673</v>
@@ -798,7 +798,7 @@
         <v>0.000704001571388549</v>
       </c>
       <c r="I21">
-        <v>-0.000768252781459263</v>
+        <v>-0.000784192766462053</v>
       </c>
       <c r="J21">
         <v>-0.000251954751417673</v>
@@ -814,19 +814,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>3.86991549916615e-11</v>
+        <v>4.98133900410944e-09</v>
       </c>
       <c r="C22">
-        <v>-0.00882115784614664</v>
+        <v>-0.00917698054555719</v>
       </c>
       <c r="D22">
-        <v>-0.00908439499991282</v>
+        <v>-0.00944021769932337</v>
       </c>
       <c r="E22">
-        <v>0.00977904456002373</v>
+        <v>0.0101348672594343</v>
       </c>
       <c r="F22">
-        <v>0.00882115784614664</v>
+        <v>0.00917698054555719</v>
       </c>
       <c r="G22">
         <v>-0.000263237153766178</v>
@@ -835,7 +835,7 @@
         <v>0.000957886713877087</v>
       </c>
       <c r="I22">
-        <v>0.00908439499991282</v>
+        <v>0.00944021769932337</v>
       </c>
       <c r="J22">
         <v>0.000263237153766178</v>
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>4.62348825891468e-10</v>
+        <v>3.32157791602655e-08</v>
       </c>
       <c r="C23">
-        <v>-0.00930772543610406</v>
+        <v>-0.00873855216819461</v>
       </c>
       <c r="D23">
-        <v>-0.0072721072605678</v>
+        <v>-0.00670293399265835</v>
       </c>
       <c r="E23">
-        <v>0.00962274415152413</v>
+        <v>0.00905357088361468</v>
       </c>
       <c r="F23">
-        <v>0.00930772543610406</v>
+        <v>0.00873855216819461</v>
       </c>
       <c r="G23">
         <v>0.00203561817553626</v>
@@ -872,7 +872,7 @@
         <v>0.000315018715420073</v>
       </c>
       <c r="I23">
-        <v>0.0072721072605678</v>
+        <v>0.00670293399265835</v>
       </c>
       <c r="J23">
         <v>-0.00203561817553626</v>
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>6.80875256175995e-09</v>
+        <v>6.43740287467939e-09</v>
       </c>
       <c r="C24">
-        <v>-0.0144235068494579</v>
+        <v>-0.0143003466234534</v>
       </c>
       <c r="D24">
-        <v>-0.0159311635153634</v>
+        <v>-0.015808003289359</v>
       </c>
       <c r="E24">
-        <v>0.0167120184217181</v>
+        <v>0.0165888581957136</v>
       </c>
       <c r="F24">
-        <v>0.0144235068494579</v>
+        <v>0.0143003466234534</v>
       </c>
       <c r="G24">
         <v>-0.00150765666590554</v>
@@ -909,7 +909,7 @@
         <v>0.00228851157226018</v>
       </c>
       <c r="I24">
-        <v>0.0159311635153634</v>
+        <v>0.015808003289359</v>
       </c>
       <c r="J24">
         <v>0.00150765666590554</v>
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>7.97397259333366e-10</v>
+        <v>0.00232390701351234</v>
       </c>
       <c r="C25">
-        <v>-0.000740279478902396</v>
+        <v>-0.000327236320507447</v>
       </c>
       <c r="D25">
-        <v>0.0016606194632394</v>
+        <v>0.00207366262163435</v>
       </c>
       <c r="E25">
-        <v>0.00176348005022321</v>
+        <v>0.00135043689182826</v>
       </c>
       <c r="F25">
-        <v>0.000740279478902396</v>
+        <v>0.000327236320507447</v>
       </c>
       <c r="G25">
         <v>0.00240089894214179</v>
@@ -946,7 +946,7 @@
         <v>0.00102320057132082</v>
       </c>
       <c r="I25">
-        <v>-0.0016606194632394</v>
+        <v>-0.00207366262163435</v>
       </c>
       <c r="J25">
         <v>-0.00240089894214179</v>
@@ -962,19 +962,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.0680345496894e-13</v>
+        <v>2.6358497291547e-10</v>
       </c>
       <c r="C26">
-        <v>-0.00750234832958085</v>
+        <v>-0.00774134592523166</v>
       </c>
       <c r="D26">
-        <v>-0.00697953360421317</v>
+        <v>-0.00721853119986398</v>
       </c>
       <c r="E26">
-        <v>0.00796192032950265</v>
+        <v>0.00820091792515346</v>
       </c>
       <c r="F26">
-        <v>0.00750234832958085</v>
+        <v>0.00774134592523166</v>
       </c>
       <c r="G26">
         <v>0.000522814725367685</v>
@@ -983,7 +983,7 @@
         <v>0.000459571999921796</v>
       </c>
       <c r="I26">
-        <v>0.00697953360421317</v>
+        <v>0.00721853119986398</v>
       </c>
       <c r="J26">
         <v>-0.000522814725367685</v>
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.84297473948547e-08</v>
+        <v>3.35118673566762e-08</v>
       </c>
       <c r="C27">
-        <v>-0.0137640184303954</v>
+        <v>-0.0126044185812394</v>
       </c>
       <c r="D27">
-        <v>-0.0121470178876605</v>
+        <v>-0.0109874180385045</v>
       </c>
       <c r="E27">
-        <v>0.0164191722869873</v>
+        <v>0.0152595724378313</v>
       </c>
       <c r="F27">
-        <v>0.0137640184303954</v>
+        <v>0.0126044185812394</v>
       </c>
       <c r="G27">
         <v>0.00161700054273492</v>
@@ -1020,7 +1020,7 @@
         <v>0.00265515385659195</v>
       </c>
       <c r="I27">
-        <v>0.0121470178876605</v>
+        <v>0.0109874180385045</v>
       </c>
       <c r="J27">
         <v>-0.00161700054273492</v>
@@ -1036,19 +1036,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.00417047903254708</v>
+        <v>0.000376334456797562</v>
       </c>
       <c r="C28">
-        <v>0.000234766217805113</v>
+        <v>0.00033067860619797</v>
       </c>
       <c r="D28">
-        <v>-3.47069331577849e-05</v>
+        <v>6.12054552350722e-05</v>
       </c>
       <c r="E28">
-        <v>0.000663042068481445</v>
+        <v>0.000567129680088588</v>
       </c>
       <c r="F28">
-        <v>-0.000234766217805113</v>
+        <v>-0.00033067860619797</v>
       </c>
       <c r="G28">
         <v>-0.000269473150962897</v>
@@ -1057,7 +1057,7 @@
         <v>0.000897808286286558</v>
       </c>
       <c r="I28">
-        <v>3.47069331577849e-05</v>
+        <v>-6.12054552350722e-05</v>
       </c>
       <c r="J28">
         <v>0.000269473150962897</v>
@@ -1073,19 +1073,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>6.38050767776122e-07</v>
+        <v>4.81541860656642e-07</v>
       </c>
       <c r="C29">
-        <v>-0.00991980252157579</v>
+        <v>-0.0111974876869811</v>
       </c>
       <c r="D29">
-        <v>-0.00835251808166502</v>
+        <v>-0.00963020324707031</v>
       </c>
       <c r="E29">
-        <v>0.0146941798073905</v>
+        <v>0.0159718649727958</v>
       </c>
       <c r="F29">
-        <v>0.00991980252157579</v>
+        <v>0.0111974876869811</v>
       </c>
       <c r="G29">
         <v>0.00156728443991077</v>
@@ -1094,7 +1094,7 @@
         <v>0.00477437728581468</v>
       </c>
       <c r="I29">
-        <v>0.00835251808166502</v>
+        <v>0.00963020324707031</v>
       </c>
       <c r="J29">
         <v>-0.00156728443991077</v>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>6.30007554655734e-18</v>
       </c>
       <c r="C30">
-        <v>0.0235695300886748</v>
+        <v>0.0256519120183449</v>
       </c>
       <c r="D30">
-        <v>-0.0106898035321917</v>
+        <v>-0.00860742160252161</v>
       </c>
       <c r="E30">
-        <v>0.0127302919115339</v>
+        <v>0.0106479099818638</v>
       </c>
       <c r="F30">
-        <v>-0.0235695300886748</v>
+        <v>-0.0256519120183449</v>
       </c>
       <c r="G30">
         <v>-0.0342593336208665</v>
@@ -1131,7 +1131,7 @@
         <v>0.0362998220002087</v>
       </c>
       <c r="I30">
-        <v>0.0106898035321917</v>
+        <v>0.00860742160252161</v>
       </c>
       <c r="J30">
         <v>0.0342593336208665</v>
@@ -1147,19 +1147,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>8.94061105286559e-05</v>
+        <v>0.0051862072420036</v>
       </c>
       <c r="C31">
-        <v>-0.00588160792800149</v>
+        <v>-0.00238577848202632</v>
       </c>
       <c r="D31">
-        <v>-0.00813160623822893</v>
+        <v>-0.00463577679225376</v>
       </c>
       <c r="E31">
-        <v>0.0155210494995117</v>
+        <v>0.0120252200535366</v>
       </c>
       <c r="F31">
-        <v>0.00588160792800149</v>
+        <v>0.00238577848202632</v>
       </c>
       <c r="G31">
         <v>-0.00224999831022744</v>
@@ -1168,7 +1168,7 @@
         <v>0.00963944157151023</v>
       </c>
       <c r="I31">
-        <v>0.00813160623822893</v>
+        <v>0.00463577679225376</v>
       </c>
       <c r="J31">
         <v>0.00224999831022744</v>
@@ -1184,19 +1184,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>2.18244893746e-06</v>
+        <v>2.37569733171961e-07</v>
       </c>
       <c r="C32">
-        <v>-0.00381076735668882</v>
+        <v>-0.00407251689674532</v>
       </c>
       <c r="D32">
-        <v>-0.00233234677995954</v>
+        <v>-0.00259409632001604</v>
       </c>
       <c r="E32">
-        <v>0.00625113078526088</v>
+        <v>0.00651288032531738</v>
       </c>
       <c r="F32">
-        <v>0.00381076735668882</v>
+        <v>0.00407251689674532</v>
       </c>
       <c r="G32">
         <v>0.00147842057672928</v>
@@ -1205,7 +1205,7 @@
         <v>0.00244036342857206</v>
       </c>
       <c r="I32">
-        <v>0.00233234677995954</v>
+        <v>0.00259409632001604</v>
       </c>
       <c r="J32">
         <v>-0.00147842057672928</v>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.00862142227154e-06</v>
+        <v>7.44551556659188e-07</v>
       </c>
       <c r="C33">
-        <v>-0.00170790166885126</v>
+        <v>-0.00156944859398728</v>
       </c>
       <c r="D33">
-        <v>-0.00219719750540597</v>
+        <v>-0.00205874443054199</v>
       </c>
       <c r="E33">
-        <v>0.00395846366882324</v>
+        <v>0.00382001059395926</v>
       </c>
       <c r="F33">
-        <v>0.00170790166885126</v>
+        <v>0.00156944859398728</v>
       </c>
       <c r="G33">
         <v>-0.000489295836554707</v>
@@ -1242,7 +1242,7 @@
         <v>0.00225056199997198</v>
       </c>
       <c r="I33">
-        <v>0.00219719750540597</v>
+        <v>0.00205874443054199</v>
       </c>
       <c r="J33">
         <v>0.000489295836554707</v>

--- a/lang.compare.xlsx
+++ b/lang.compare.xlsx
@@ -74,19 +74,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>2.8880773738412e-06</v>
+        <v>3.41194150978943e-06</v>
       </c>
       <c r="C2">
-        <v>0.000161838751539887</v>
+        <v>0.000155605808686232</v>
       </c>
       <c r="D2">
-        <v>8.37189810616629e-05</v>
+        <v>7.74860382080078e-05</v>
       </c>
       <c r="E2">
-        <v>0.000102179391043527</v>
+        <v>0.000108412333897182</v>
       </c>
       <c r="F2">
-        <v>-0.000161838751539887</v>
+        <v>-0.000155605808686232</v>
       </c>
       <c r="G2">
         <v>-7.81197704782244e-05</v>
@@ -95,7 +95,7 @@
         <v>0.000264018142583414</v>
       </c>
       <c r="I2">
-        <v>-8.37189810616629e-05</v>
+        <v>-7.74860382080078e-05</v>
       </c>
       <c r="J2">
         <v>7.81197704782244e-05</v>
@@ -111,19 +111,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.133146839472534</v>
+        <v>0.345573691806443</v>
       </c>
       <c r="C3">
-        <v>4.20369183952321e-05</v>
+        <v>3.51227796012869e-05</v>
       </c>
       <c r="D3">
-        <v>-2.96660831996375e-05</v>
+        <v>-3.65802219935827e-05</v>
       </c>
       <c r="E3">
-        <v>0.000355958938598633</v>
+        <v>0.000362873077392578</v>
       </c>
       <c r="F3">
-        <v>-4.20369183952321e-05</v>
+        <v>-3.51227796012869e-05</v>
       </c>
       <c r="G3">
         <v>-7.17030015948696e-05</v>
@@ -132,7 +132,7 @@
         <v>0.000397995856993865</v>
       </c>
       <c r="I3">
-        <v>2.96660831996375e-05</v>
+        <v>3.65802219935827e-05</v>
       </c>
       <c r="J3">
         <v>7.17030015948696e-05</v>
@@ -148,19 +148,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.000908219851103137</v>
+        <v>0.00146882919769204</v>
       </c>
       <c r="C4">
-        <v>0.000143990700702748</v>
+        <v>0.000133874940989439</v>
       </c>
       <c r="D4">
-        <v>-5.79016549246601e-07</v>
+        <v>-1.06947762625559e-05</v>
       </c>
       <c r="E4">
-        <v>0.000193016869681222</v>
+        <v>0.000203132629394531</v>
       </c>
       <c r="F4">
-        <v>-0.000143990700702748</v>
+        <v>-0.000133874940989439</v>
       </c>
       <c r="G4">
         <v>-0.000144569717251995</v>
@@ -169,7 +169,7 @@
         <v>0.00033700757038397</v>
       </c>
       <c r="I4">
-        <v>5.79016549246601e-07</v>
+        <v>1.06947762625559e-05</v>
       </c>
       <c r="J4">
         <v>0.000144569717251995</v>
@@ -185,19 +185,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>5.14921587447615e-05</v>
+        <v>0.000142037219527596</v>
       </c>
       <c r="C5">
-        <v>0.000118229851068463</v>
+        <v>0.000103107301194021</v>
       </c>
       <c r="D5">
-        <v>1.12737928118025e-05</v>
+        <v>-3.84875706263958e-06</v>
       </c>
       <c r="E5">
-        <v>0.000184876578194754</v>
+        <v>0.000199999128069196</v>
       </c>
       <c r="F5">
-        <v>-0.000118229851068463</v>
+        <v>-0.000103107301194021</v>
       </c>
       <c r="G5">
         <v>-0.000106956058256661</v>
@@ -206,7 +206,7 @@
         <v>0.000303106429263218</v>
       </c>
       <c r="I5">
-        <v>-1.12737928118025e-05</v>
+        <v>3.84875706263958e-06</v>
       </c>
       <c r="J5">
         <v>0.000106956058256661</v>
@@ -222,19 +222,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.07732810112514e-06</v>
+        <v>1.71113092849417e-06</v>
       </c>
       <c r="C6">
-        <v>0.000135010961197882</v>
+        <v>0.000126223533568139</v>
       </c>
       <c r="D6">
-        <v>2.5510787963867e-05</v>
+        <v>1.67233603341238e-05</v>
       </c>
       <c r="E6">
-        <v>0.000126634325299944</v>
+        <v>0.000135421752929688</v>
       </c>
       <c r="F6">
-        <v>-0.000135010961197882</v>
+        <v>-0.000126223533568139</v>
       </c>
       <c r="G6">
         <v>-0.000109500173234015</v>
@@ -243,7 +243,7 @@
         <v>0.000261645286497826</v>
       </c>
       <c r="I6">
-        <v>-2.5510787963867e-05</v>
+        <v>-1.67233603341238e-05</v>
       </c>
       <c r="J6">
         <v>0.000109500173234015</v>
@@ -259,19 +259,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>6.45277429127434e-07</v>
+        <v>5.78951123156115e-07</v>
       </c>
       <c r="C7">
-        <v>0.000109921466251503</v>
+        <v>0.000105425573045588</v>
       </c>
       <c r="D7">
-        <v>1.43051147460937e-05</v>
+        <v>9.8092215401787e-06</v>
       </c>
       <c r="E7">
-        <v>0.000130414962768555</v>
+        <v>0.00013491085597447</v>
       </c>
       <c r="F7">
-        <v>-0.000109921466251503</v>
+        <v>-0.000105425573045588</v>
       </c>
       <c r="G7">
         <v>-9.56163515054089e-05</v>
@@ -280,7 +280,7 @@
         <v>0.000240336429020057</v>
       </c>
       <c r="I7">
-        <v>-1.43051147460937e-05</v>
+        <v>-9.8092215401787e-06</v>
       </c>
       <c r="J7">
         <v>9.56163515054089e-05</v>
@@ -296,19 +296,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.11607514619256e-06</v>
+        <v>3.63827033029257e-07</v>
       </c>
       <c r="C8">
-        <v>-0.00112564872012756</v>
+        <v>-0.00121008295692653</v>
       </c>
       <c r="D8">
-        <v>-0.00114478383745466</v>
+        <v>-0.00122921807425363</v>
       </c>
       <c r="E8">
-        <v>0.00180251257760184</v>
+        <v>0.00188694681440081</v>
       </c>
       <c r="F8">
-        <v>0.00112564872012756</v>
+        <v>0.00121008295692653</v>
       </c>
       <c r="G8">
         <v>-1.91351173270965e-05</v>
@@ -317,7 +317,7 @@
         <v>0.000676863857474278</v>
       </c>
       <c r="I8">
-        <v>0.00114478383745466</v>
+        <v>0.00122921807425363</v>
       </c>
       <c r="J8">
         <v>1.91351173270965e-05</v>
@@ -333,19 +333,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.00195854527598812</v>
+        <v>0.00247872864795966</v>
       </c>
       <c r="C9">
-        <v>0.000107210652848673</v>
+        <v>0.000104383689696468</v>
       </c>
       <c r="D9">
-        <v>-0.000139951705932618</v>
+        <v>-0.000142778669084822</v>
       </c>
       <c r="E9">
-        <v>0.000454323632376534</v>
+        <v>0.000457150595528739</v>
       </c>
       <c r="F9">
-        <v>-0.000107210652848673</v>
+        <v>-0.000104383689696468</v>
       </c>
       <c r="G9">
         <v>-0.00024716235878129</v>
@@ -354,7 +354,7 @@
         <v>0.000561534285225207</v>
       </c>
       <c r="I9">
-        <v>0.000139951705932618</v>
+        <v>0.000142778669084822</v>
       </c>
       <c r="J9">
         <v>0.00024716235878129</v>
@@ -370,19 +370,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.000107178562171379</v>
+        <v>1.56738721540149e-06</v>
       </c>
       <c r="C10">
-        <v>-9.4091409534615e-05</v>
+        <v>-0.00010795374691952</v>
       </c>
       <c r="D10">
-        <v>-0.00024512835911342</v>
+        <v>-0.000258990696498325</v>
       </c>
       <c r="E10">
-        <v>0.000514166695731027</v>
+        <v>0.000528029033115932</v>
       </c>
       <c r="F10">
-        <v>9.4091409534615e-05</v>
+        <v>0.00010795374691952</v>
       </c>
       <c r="G10">
         <v>-0.000151036949578805</v>
@@ -391,7 +391,7 @@
         <v>0.000420075286196412</v>
       </c>
       <c r="I10">
-        <v>0.00024512835911342</v>
+        <v>0.000258990696498325</v>
       </c>
       <c r="J10">
         <v>0.000151036949578805</v>
@@ -407,19 +407,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>3.52053190532094e-09</v>
+        <v>1.29677048849528e-08</v>
       </c>
       <c r="C11">
-        <v>-0.000126609231561555</v>
+        <v>-0.000122964833281003</v>
       </c>
       <c r="D11">
-        <v>-2.68731798444475e-05</v>
+        <v>-2.32287815638951e-05</v>
       </c>
       <c r="E11">
-        <v>0.000162465231759208</v>
+        <v>0.000158820833478655</v>
       </c>
       <c r="F11">
-        <v>0.000126609231561555</v>
+        <v>0.000122964833281003</v>
       </c>
       <c r="G11">
         <v>9.97360517171078e-05</v>
@@ -428,7 +428,7 @@
         <v>3.58560001976522e-05</v>
       </c>
       <c r="I11">
-        <v>2.68731798444475e-05</v>
+        <v>2.32287815638951e-05</v>
       </c>
       <c r="J11">
         <v>-9.97360517171078e-05</v>
@@ -444,19 +444,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>6.01729571975434e-09</v>
+        <v>2.34660800835089e-11</v>
       </c>
       <c r="C12">
-        <v>-0.000101152133928346</v>
+        <v>-0.000116989939540092</v>
       </c>
       <c r="D12">
-        <v>-8.37871006556911e-06</v>
+        <v>-2.42165156773158e-05</v>
       </c>
       <c r="E12">
-        <v>0.000124897275652204</v>
+        <v>0.000140735081263951</v>
       </c>
       <c r="F12">
-        <v>0.000101152133928346</v>
+        <v>0.000116989939540092</v>
       </c>
       <c r="G12">
         <v>9.27734238627766e-05</v>
@@ -465,7 +465,7 @@
         <v>2.37451417238585e-05</v>
       </c>
       <c r="I12">
-        <v>8.37871006556911e-06</v>
+        <v>2.42165156773158e-05</v>
       </c>
       <c r="J12">
         <v>-9.27734238627766e-05</v>
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>3.05110607619447e-07</v>
+        <v>1.26387326723506e-06</v>
       </c>
       <c r="C13">
-        <v>-0.00252167170505605</v>
+        <v>-0.00253771386944988</v>
       </c>
       <c r="D13">
-        <v>-0.00375710214887346</v>
+        <v>-0.0037731443132673</v>
       </c>
       <c r="E13">
-        <v>0.00535072599138532</v>
+        <v>0.00536676815577916</v>
       </c>
       <c r="F13">
-        <v>0.00252167170505605</v>
+        <v>0.00253771386944988</v>
       </c>
       <c r="G13">
         <v>-0.00123543044381742</v>
@@ -502,7 +502,7 @@
         <v>0.00282905428632928</v>
       </c>
       <c r="I13">
-        <v>0.00375710214887346</v>
+        <v>0.0037731443132673</v>
       </c>
       <c r="J13">
         <v>0.00123543044381742</v>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>2.32319725135296e-12</v>
+        <v>2.75896980321785e-13</v>
       </c>
       <c r="C14">
-        <v>-0.00398948282132291</v>
+        <v>-0.00410058587918424</v>
       </c>
       <c r="D14">
-        <v>0.0043708937508719</v>
+        <v>0.00425979069301057</v>
       </c>
       <c r="E14">
-        <v>0.007566009249006</v>
+        <v>0.00767711230686733</v>
       </c>
       <c r="F14">
-        <v>0.00398948282132291</v>
+        <v>0.00410058587918424</v>
       </c>
       <c r="G14">
         <v>0.00836037657219481</v>
@@ -539,7 +539,7 @@
         <v>0.00357652642768309</v>
       </c>
       <c r="I14">
-        <v>-0.0043708937508719</v>
+        <v>-0.00425979069301057</v>
       </c>
       <c r="J14">
         <v>-0.00836037657219481</v>
@@ -555,19 +555,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>4.65343068519643e-09</v>
+        <v>1.36667007950072e-09</v>
       </c>
       <c r="C15">
-        <v>-0.0099132710077226</v>
+        <v>-0.00902461684381705</v>
       </c>
       <c r="D15">
-        <v>-0.0147398199353899</v>
+        <v>-0.0138511657714844</v>
       </c>
       <c r="E15">
-        <v>0.0160148484366281</v>
+        <v>0.0151261942727225</v>
       </c>
       <c r="F15">
-        <v>0.0099132710077226</v>
+        <v>0.00902461684381705</v>
       </c>
       <c r="G15">
         <v>-0.00482654892766732</v>
@@ -576,7 +576,7 @@
         <v>0.00610157742890546</v>
       </c>
       <c r="I15">
-        <v>0.0147398199353899</v>
+        <v>0.0138511657714844</v>
       </c>
       <c r="J15">
         <v>0.00482654892766732</v>
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>6.23875917135205e-05</v>
+        <v>2.52393284925888e-11</v>
       </c>
       <c r="C16">
-        <v>-0.000677243627121373</v>
+        <v>-0.000742195660028042</v>
       </c>
       <c r="D16">
-        <v>-0.000725984573364259</v>
+        <v>-0.000790936606270928</v>
       </c>
       <c r="E16">
-        <v>0.00133531434195382</v>
+        <v>0.00140026637486049</v>
       </c>
       <c r="F16">
-        <v>0.000677243627121373</v>
+        <v>0.000742195660028042</v>
       </c>
       <c r="G16">
         <v>-4.87409462428857e-05</v>
@@ -613,7 +613,7 @@
         <v>0.00065807071483245</v>
       </c>
       <c r="I16">
-        <v>0.000725984573364259</v>
+        <v>0.000790936606270928</v>
       </c>
       <c r="J16">
         <v>4.87409462428857e-05</v>
@@ -629,19 +629,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.255692927982255</v>
+        <v>0.0853522007367718</v>
       </c>
       <c r="C17">
-        <v>-4.92193991833897e-05</v>
+        <v>-3.49824040313249e-05</v>
       </c>
       <c r="D17">
-        <v>-1.84604099818637e-05</v>
+        <v>-4.2234148297988e-06</v>
       </c>
       <c r="E17">
-        <v>0.000278268541608538</v>
+        <v>0.000264031546456473</v>
       </c>
       <c r="F17">
-        <v>4.92193991833897e-05</v>
+        <v>3.49824040313249e-05</v>
       </c>
       <c r="G17">
         <v>3.07589892015261e-05</v>
@@ -650,7 +650,7 @@
         <v>0.000229049142425148</v>
       </c>
       <c r="I17">
-        <v>1.84604099818637e-05</v>
+        <v>4.2234148297988e-06</v>
       </c>
       <c r="J17">
         <v>-3.07589892015261e-05</v>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>4.99280739001676e-10</v>
+        <v>4.92037927491457e-13</v>
       </c>
       <c r="C18">
-        <v>-0.00240758479464733</v>
+        <v>-0.00225455412666114</v>
       </c>
       <c r="D18">
-        <v>-0.0017869131905692</v>
+        <v>-0.00163388252258301</v>
       </c>
       <c r="E18">
-        <v>0.00328104836600167</v>
+        <v>0.00312801769801549</v>
       </c>
       <c r="F18">
-        <v>0.00240758479464733</v>
+        <v>0.00225455412666114</v>
       </c>
       <c r="G18">
         <v>0.00062067160407813</v>
@@ -687,7 +687,7 @@
         <v>0.000873463571354348</v>
       </c>
       <c r="I18">
-        <v>0.0017869131905692</v>
+        <v>0.00163388252258301</v>
       </c>
       <c r="J18">
         <v>-0.00062067160407813</v>
@@ -703,19 +703,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.53631059709857e-10</v>
+        <v>5.67049798405038e-10</v>
       </c>
       <c r="C19">
-        <v>0.000742848532744185</v>
+        <v>0.000702181135108861</v>
       </c>
       <c r="D19">
-        <v>0.00144774573189872</v>
+        <v>0.00140707833426339</v>
       </c>
       <c r="E19">
-        <v>0.000133957181658063</v>
+        <v>0.000174624579293387</v>
       </c>
       <c r="F19">
-        <v>-0.000742848532744185</v>
+        <v>-0.000702181135108861</v>
       </c>
       <c r="G19">
         <v>0.000704897199154532</v>
@@ -724,7 +724,7 @@
         <v>0.000876805714402248</v>
       </c>
       <c r="I19">
-        <v>-0.00144774573189872</v>
+        <v>-0.00140707833426339</v>
       </c>
       <c r="J19">
         <v>-0.000704897199154532</v>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.35604234407254e-09</v>
+        <v>9.95485484357194e-10</v>
       </c>
       <c r="C20">
-        <v>0.000596541162459679</v>
+        <v>0.000578148872071844</v>
       </c>
       <c r="D20">
-        <v>0.00092686925615583</v>
+        <v>0.000908476965767995</v>
       </c>
       <c r="E20">
-        <v>0.000153371265956334</v>
+        <v>0.000171763556344168</v>
       </c>
       <c r="F20">
-        <v>-0.000596541162459679</v>
+        <v>-0.000578148872071844</v>
       </c>
       <c r="G20">
         <v>0.000330328093696152</v>
@@ -761,7 +761,7 @@
         <v>0.000749912428416012</v>
       </c>
       <c r="I20">
-        <v>-0.00092686925615583</v>
+        <v>-0.000908476965767995</v>
       </c>
       <c r="J20">
         <v>-0.000330328093696152</v>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.69214147340278e-08</v>
+        <v>2.56135962415844e-08</v>
       </c>
       <c r="C21">
-        <v>0.000532238015044381</v>
+        <v>0.000508600515916312</v>
       </c>
       <c r="D21">
-        <v>0.000784192766462053</v>
+        <v>0.000760555267333984</v>
       </c>
       <c r="E21">
-        <v>0.000171763556344169</v>
+        <v>0.000195401055472238</v>
       </c>
       <c r="F21">
-        <v>-0.000532238015044381</v>
+        <v>-0.000508600515916312</v>
       </c>
       <c r="G21">
         <v>0.000251954751417673</v>
@@ -798,7 +798,7 @@
         <v>0.000704001571388549</v>
       </c>
       <c r="I21">
-        <v>-0.000784192766462053</v>
+        <v>-0.000760555267333984</v>
       </c>
       <c r="J21">
         <v>-0.000251954751417673</v>
@@ -814,19 +814,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>4.98133900410944e-09</v>
+        <v>7.22424468178975e-11</v>
       </c>
       <c r="C22">
-        <v>-0.00917698054555719</v>
+        <v>-0.00893348705670048</v>
       </c>
       <c r="D22">
-        <v>-0.00944021769932337</v>
+        <v>-0.00919672421046665</v>
       </c>
       <c r="E22">
-        <v>0.0101348672594343</v>
+        <v>0.00989137377057756</v>
       </c>
       <c r="F22">
-        <v>0.00917698054555719</v>
+        <v>0.00893348705670048</v>
       </c>
       <c r="G22">
         <v>-0.000263237153766178</v>
@@ -835,7 +835,7 @@
         <v>0.000957886713877087</v>
       </c>
       <c r="I22">
-        <v>0.00944021769932337</v>
+        <v>0.00919672421046665</v>
       </c>
       <c r="J22">
         <v>0.000263237153766178</v>
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>3.32157791602655e-08</v>
+        <v>7.55942930251676e-09</v>
       </c>
       <c r="C23">
-        <v>-0.00873855216819461</v>
+        <v>-0.0104101048262757</v>
       </c>
       <c r="D23">
-        <v>-0.00670293399265835</v>
+        <v>-0.0083744866507394</v>
       </c>
       <c r="E23">
-        <v>0.00905357088361468</v>
+        <v>0.0107251235416957</v>
       </c>
       <c r="F23">
-        <v>0.00873855216819461</v>
+        <v>0.0104101048262757</v>
       </c>
       <c r="G23">
         <v>0.00203561817553626</v>
@@ -872,7 +872,7 @@
         <v>0.000315018715420073</v>
       </c>
       <c r="I23">
-        <v>0.00670293399265835</v>
+        <v>0.0083744866507394</v>
       </c>
       <c r="J23">
         <v>-0.00203561817553626</v>
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>6.43740287467939e-09</v>
+        <v>4.55455208219234e-08</v>
       </c>
       <c r="C24">
-        <v>-0.0143003466234534</v>
+        <v>-0.0144296376129205</v>
       </c>
       <c r="D24">
-        <v>-0.015808003289359</v>
+        <v>-0.015937294278826</v>
       </c>
       <c r="E24">
-        <v>0.0165888581957136</v>
+        <v>0.0167181491851807</v>
       </c>
       <c r="F24">
-        <v>0.0143003466234534</v>
+        <v>0.0144296376129205</v>
       </c>
       <c r="G24">
         <v>-0.00150765666590554</v>
@@ -909,7 +909,7 @@
         <v>0.00228851157226018</v>
       </c>
       <c r="I24">
-        <v>0.015808003289359</v>
+        <v>0.015937294278826</v>
       </c>
       <c r="J24">
         <v>0.00150765666590554</v>
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.00232390701351234</v>
+        <v>7.51415478459592e-07</v>
       </c>
       <c r="C25">
-        <v>-0.000327236320507447</v>
+        <v>-0.000510852686212662</v>
       </c>
       <c r="D25">
-        <v>0.00207366262163435</v>
+        <v>0.00189004625592913</v>
       </c>
       <c r="E25">
-        <v>0.00135043689182826</v>
+        <v>0.00153405325753348</v>
       </c>
       <c r="F25">
-        <v>0.000327236320507447</v>
+        <v>0.000510852686212662</v>
       </c>
       <c r="G25">
         <v>0.00240089894214179</v>
@@ -946,7 +946,7 @@
         <v>0.00102320057132082</v>
       </c>
       <c r="I25">
-        <v>-0.00207366262163435</v>
+        <v>-0.00189004625592913</v>
       </c>
       <c r="J25">
         <v>-0.00240089894214179</v>
@@ -962,19 +962,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>2.6358497291547e-10</v>
+        <v>3.92800461075416e-13</v>
       </c>
       <c r="C26">
-        <v>-0.00774134592523166</v>
+        <v>-0.00786460833062717</v>
       </c>
       <c r="D26">
-        <v>-0.00721853119986398</v>
+        <v>-0.00734179360525949</v>
       </c>
       <c r="E26">
-        <v>0.00820091792515346</v>
+        <v>0.00832418033054897</v>
       </c>
       <c r="F26">
-        <v>0.00774134592523166</v>
+        <v>0.00786460833062717</v>
       </c>
       <c r="G26">
         <v>0.000522814725367685</v>
@@ -983,7 +983,7 @@
         <v>0.000459571999921796</v>
       </c>
       <c r="I26">
-        <v>0.00721853119986398</v>
+        <v>0.00734179360525949</v>
       </c>
       <c r="J26">
         <v>-0.000522814725367685</v>
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>3.35118673566762e-08</v>
+        <v>2.13110974206695e-08</v>
       </c>
       <c r="C27">
-        <v>-0.0126044185812394</v>
+        <v>-0.0131102746864989</v>
       </c>
       <c r="D27">
-        <v>-0.0109874180385045</v>
+        <v>-0.011493274143764</v>
       </c>
       <c r="E27">
-        <v>0.0152595724378313</v>
+        <v>0.0157654285430908</v>
       </c>
       <c r="F27">
-        <v>0.0126044185812394</v>
+        <v>0.0131102746864989</v>
       </c>
       <c r="G27">
         <v>0.00161700054273492</v>
@@ -1020,7 +1020,7 @@
         <v>0.00265515385659195</v>
       </c>
       <c r="I27">
-        <v>0.0109874180385045</v>
+        <v>0.011493274143764</v>
       </c>
       <c r="J27">
         <v>-0.00161700054273492</v>
@@ -1036,19 +1036,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.000376334456797562</v>
+        <v>0.00088769315453808</v>
       </c>
       <c r="C28">
-        <v>0.00033067860619797</v>
+        <v>0.000301080642592361</v>
       </c>
       <c r="D28">
-        <v>6.12054552350722e-05</v>
+        <v>3.1607491629464e-05</v>
       </c>
       <c r="E28">
-        <v>0.000567129680088588</v>
+        <v>0.000596727643694196</v>
       </c>
       <c r="F28">
-        <v>-0.00033067860619797</v>
+        <v>-0.000301080642592361</v>
       </c>
       <c r="G28">
         <v>-0.000269473150962897</v>
@@ -1057,7 +1057,7 @@
         <v>0.000897808286286558</v>
       </c>
       <c r="I28">
-        <v>-6.12054552350722e-05</v>
+        <v>-3.1607491629464e-05</v>
       </c>
       <c r="J28">
         <v>0.000269473150962897</v>
@@ -1073,19 +1073,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>4.81541860656642e-07</v>
+        <v>4.90886128769323e-07</v>
       </c>
       <c r="C29">
-        <v>-0.0111974876869811</v>
+        <v>-0.0130527588901584</v>
       </c>
       <c r="D29">
-        <v>-0.00963020324707031</v>
+        <v>-0.0114854744502477</v>
       </c>
       <c r="E29">
-        <v>0.0159718649727958</v>
+        <v>0.0178271361759731</v>
       </c>
       <c r="F29">
-        <v>0.0111974876869811</v>
+        <v>0.0130527588901584</v>
       </c>
       <c r="G29">
         <v>0.00156728443991077</v>
@@ -1094,7 +1094,7 @@
         <v>0.00477437728581468</v>
       </c>
       <c r="I29">
-        <v>0.00963020324707031</v>
+        <v>0.0114854744502477</v>
       </c>
       <c r="J29">
         <v>-0.00156728443991077</v>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>6.30007554655734e-18</v>
+        <v>9.68699773368917e-19</v>
       </c>
       <c r="C30">
-        <v>0.0256519120183449</v>
+        <v>0.0239285544090048</v>
       </c>
       <c r="D30">
-        <v>-0.00860742160252161</v>
+        <v>-0.0103307792118617</v>
       </c>
       <c r="E30">
-        <v>0.0106479099818638</v>
+        <v>0.0123712675912039</v>
       </c>
       <c r="F30">
-        <v>-0.0256519120183449</v>
+        <v>-0.0239285544090048</v>
       </c>
       <c r="G30">
         <v>-0.0342593336208665</v>
@@ -1131,7 +1131,7 @@
         <v>0.0362998220002087</v>
       </c>
       <c r="I30">
-        <v>0.00860742160252161</v>
+        <v>0.0103307792118617</v>
       </c>
       <c r="J30">
         <v>0.0342593336208665</v>
@@ -1147,19 +1147,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.0051862072420036</v>
+        <v>0.00608343833347923</v>
       </c>
       <c r="C31">
-        <v>-0.00238577848202632</v>
+        <v>-0.00177798140430241</v>
       </c>
       <c r="D31">
-        <v>-0.00463577679225376</v>
+        <v>-0.00402797971452986</v>
       </c>
       <c r="E31">
-        <v>0.0120252200535366</v>
+        <v>0.0114174229758126</v>
       </c>
       <c r="F31">
-        <v>0.00238577848202632</v>
+        <v>0.00177798140430241</v>
       </c>
       <c r="G31">
         <v>-0.00224999831022744</v>
@@ -1168,7 +1168,7 @@
         <v>0.00963944157151023</v>
       </c>
       <c r="I31">
-        <v>0.00463577679225376</v>
+        <v>0.00402797971452986</v>
       </c>
       <c r="J31">
         <v>0.00224999831022744</v>
@@ -1184,19 +1184,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>2.37569733171961e-07</v>
+        <v>5.30745885736111e-14</v>
       </c>
       <c r="C32">
-        <v>-0.00407251689674532</v>
+        <v>-0.00465238494091734</v>
       </c>
       <c r="D32">
-        <v>-0.00259409632001604</v>
+        <v>-0.00317396436418806</v>
       </c>
       <c r="E32">
-        <v>0.00651288032531738</v>
+        <v>0.0070927483694894</v>
       </c>
       <c r="F32">
-        <v>0.00407251689674532</v>
+        <v>0.00465238494091734</v>
       </c>
       <c r="G32">
         <v>0.00147842057672928</v>
@@ -1205,7 +1205,7 @@
         <v>0.00244036342857206</v>
       </c>
       <c r="I32">
-        <v>0.00259409632001604</v>
+        <v>0.00317396436418806</v>
       </c>
       <c r="J32">
         <v>-0.00147842057672928</v>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>7.44551556659188e-07</v>
+        <v>5.81972028258988e-07</v>
       </c>
       <c r="C33">
-        <v>-0.00156944859398728</v>
+        <v>-0.00176859622713112</v>
       </c>
       <c r="D33">
-        <v>-0.00205874443054199</v>
+        <v>-0.00225789206368583</v>
       </c>
       <c r="E33">
-        <v>0.00382001059395926</v>
+        <v>0.0040191582271031</v>
       </c>
       <c r="F33">
-        <v>0.00156944859398728</v>
+        <v>0.00176859622713112</v>
       </c>
       <c r="G33">
         <v>-0.000489295836554707</v>
@@ -1242,7 +1242,7 @@
         <v>0.00225056199997198</v>
       </c>
       <c r="I33">
-        <v>0.00205874443054199</v>
+        <v>0.00225789206368583</v>
       </c>
       <c r="J33">
         <v>0.000489295836554707</v>

--- a/lang.compare.xlsx
+++ b/lang.compare.xlsx
@@ -74,19 +74,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>3.41194150978943e-06</v>
+        <v>9.6897475561497e-06</v>
       </c>
       <c r="C2">
-        <v>0.000155605808686232</v>
+        <v>0.000140449199014776</v>
       </c>
       <c r="D2">
-        <v>7.74860382080078e-05</v>
+        <v>6.23294285365512e-05</v>
       </c>
       <c r="E2">
-        <v>0.000108412333897182</v>
+        <v>0.000123568943568639</v>
       </c>
       <c r="F2">
-        <v>-0.000155605808686232</v>
+        <v>-0.000140449199014776</v>
       </c>
       <c r="G2">
         <v>-7.81197704782244e-05</v>
@@ -95,7 +95,7 @@
         <v>0.000264018142583414</v>
       </c>
       <c r="I2">
-        <v>-7.74860382080078e-05</v>
+        <v>-6.23294285365512e-05</v>
       </c>
       <c r="J2">
         <v>7.81197704782244e-05</v>
@@ -111,19 +111,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.345573691806443</v>
+        <v>0.223889719095167</v>
       </c>
       <c r="C3">
-        <v>3.51227796012869e-05</v>
+        <v>3.56336765565044e-05</v>
       </c>
       <c r="D3">
-        <v>-3.65802219935827e-05</v>
+        <v>-3.60693250383652e-05</v>
       </c>
       <c r="E3">
-        <v>0.000362873077392578</v>
+        <v>0.000362362180437361</v>
       </c>
       <c r="F3">
-        <v>-3.51227796012869e-05</v>
+        <v>-3.56336765565044e-05</v>
       </c>
       <c r="G3">
         <v>-7.17030015948696e-05</v>
@@ -132,7 +132,7 @@
         <v>0.000397995856993865</v>
       </c>
       <c r="I3">
-        <v>3.65802219935827e-05</v>
+        <v>3.60693250383652e-05</v>
       </c>
       <c r="J3">
         <v>7.17030015948696e-05</v>
@@ -148,19 +148,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.00146882919769204</v>
+        <v>0.00707747265391467</v>
       </c>
       <c r="C4">
-        <v>0.000133874940989439</v>
+        <v>0.000116027607353837</v>
       </c>
       <c r="D4">
-        <v>-1.06947762625559e-05</v>
+        <v>-2.85421098981583e-05</v>
       </c>
       <c r="E4">
-        <v>0.000203132629394531</v>
+        <v>0.000220979963030134</v>
       </c>
       <c r="F4">
-        <v>-0.000133874940989439</v>
+        <v>-0.000116027607353837</v>
       </c>
       <c r="G4">
         <v>-0.000144569717251995</v>
@@ -169,7 +169,7 @@
         <v>0.00033700757038397</v>
       </c>
       <c r="I4">
-        <v>1.06947762625559e-05</v>
+        <v>2.85421098981583e-05</v>
       </c>
       <c r="J4">
         <v>0.000144569717251995</v>
@@ -185,19 +185,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.000142037219527596</v>
+        <v>0.000138631091149033</v>
       </c>
       <c r="C5">
-        <v>0.000103107301194021</v>
+        <v>0.000104776231247732</v>
       </c>
       <c r="D5">
-        <v>-3.84875706263958e-06</v>
+        <v>-2.17982700892851e-06</v>
       </c>
       <c r="E5">
-        <v>0.000199999128069196</v>
+        <v>0.000198330198015485</v>
       </c>
       <c r="F5">
-        <v>-0.000103107301194021</v>
+        <v>-0.000104776231247732</v>
       </c>
       <c r="G5">
         <v>-0.000106956058256661</v>
@@ -206,7 +206,7 @@
         <v>0.000303106429263218</v>
       </c>
       <c r="I5">
-        <v>3.84875706263958e-06</v>
+        <v>2.17982700892851e-06</v>
       </c>
       <c r="J5">
         <v>0.000106956058256661</v>
@@ -222,19 +222,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.71113092849417e-06</v>
+        <v>1.38529127962958e-06</v>
       </c>
       <c r="C6">
-        <v>0.000126223533568139</v>
+        <v>0.00012721126768156</v>
       </c>
       <c r="D6">
-        <v>1.67233603341238e-05</v>
+        <v>1.77110944475446e-05</v>
       </c>
       <c r="E6">
-        <v>0.000135421752929688</v>
+        <v>0.000134434018816267</v>
       </c>
       <c r="F6">
-        <v>-0.000126223533568139</v>
+        <v>-0.00012721126768156</v>
       </c>
       <c r="G6">
         <v>-0.000109500173234015</v>
@@ -243,7 +243,7 @@
         <v>0.000261645286497826</v>
       </c>
       <c r="I6">
-        <v>-1.67233603341238e-05</v>
+        <v>-1.77110944475446e-05</v>
       </c>
       <c r="J6">
         <v>0.000109500173234015</v>
@@ -259,19 +259,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>5.78951123156115e-07</v>
+        <v>5.62768222032994e-07</v>
       </c>
       <c r="C7">
-        <v>0.000105425573045588</v>
+        <v>0.000106072709188863</v>
       </c>
       <c r="D7">
-        <v>9.8092215401787e-06</v>
+        <v>1.04563576834542e-05</v>
       </c>
       <c r="E7">
-        <v>0.00013491085597447</v>
+        <v>0.000134263719831194</v>
       </c>
       <c r="F7">
-        <v>-0.000105425573045588</v>
+        <v>-0.000106072709188863</v>
       </c>
       <c r="G7">
         <v>-9.56163515054089e-05</v>
@@ -280,7 +280,7 @@
         <v>0.000240336429020057</v>
       </c>
       <c r="I7">
-        <v>-9.8092215401787e-06</v>
+        <v>-1.04563576834542e-05</v>
       </c>
       <c r="J7">
         <v>9.56163515054089e-05</v>
@@ -296,19 +296,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>3.63827033029257e-07</v>
+        <v>9.32765843493114e-07</v>
       </c>
       <c r="C8">
-        <v>-0.00121008295692653</v>
+        <v>-0.00112912281942304</v>
       </c>
       <c r="D8">
-        <v>-0.00122921807425363</v>
+        <v>-0.00114825793675014</v>
       </c>
       <c r="E8">
-        <v>0.00188694681440081</v>
+        <v>0.00180598667689732</v>
       </c>
       <c r="F8">
-        <v>0.00121008295692653</v>
+        <v>0.00112912281942304</v>
       </c>
       <c r="G8">
         <v>-1.91351173270965e-05</v>
@@ -317,7 +317,7 @@
         <v>0.000676863857474278</v>
       </c>
       <c r="I8">
-        <v>0.00122921807425363</v>
+        <v>0.00114825793675014</v>
       </c>
       <c r="J8">
         <v>1.91351173270965e-05</v>
@@ -333,19 +333,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.00247872864795966</v>
+        <v>0.00439755937823271</v>
       </c>
       <c r="C9">
-        <v>0.000104383689696468</v>
+        <v>9.32120762757093e-05</v>
       </c>
       <c r="D9">
-        <v>-0.000142778669084822</v>
+        <v>-0.000153950282505581</v>
       </c>
       <c r="E9">
-        <v>0.000457150595528739</v>
+        <v>0.000468322208949498</v>
       </c>
       <c r="F9">
-        <v>-0.000104383689696468</v>
+        <v>-9.32120762757093e-05</v>
       </c>
       <c r="G9">
         <v>-0.00024716235878129</v>
@@ -354,7 +354,7 @@
         <v>0.000561534285225207</v>
       </c>
       <c r="I9">
-        <v>0.000142778669084822</v>
+        <v>0.000153950282505581</v>
       </c>
       <c r="J9">
         <v>0.00024716235878129</v>
@@ -370,19 +370,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.56738721540149e-06</v>
+        <v>6.21689516160339e-06</v>
       </c>
       <c r="C10">
-        <v>-0.00010795374691952</v>
+        <v>-0.000113641733020943</v>
       </c>
       <c r="D10">
-        <v>-0.000258990696498325</v>
+        <v>-0.000264678682599748</v>
       </c>
       <c r="E10">
-        <v>0.000528029033115932</v>
+        <v>0.000533717019217355</v>
       </c>
       <c r="F10">
-        <v>0.00010795374691952</v>
+        <v>0.000113641733020943</v>
       </c>
       <c r="G10">
         <v>-0.000151036949578805</v>
@@ -391,7 +391,7 @@
         <v>0.000420075286196412</v>
       </c>
       <c r="I10">
-        <v>0.000258990696498325</v>
+        <v>0.000264678682599748</v>
       </c>
       <c r="J10">
         <v>0.000151036949578805</v>
@@ -407,19 +407,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.29677048849528e-08</v>
+        <v>6.24791903552788e-08</v>
       </c>
       <c r="C11">
-        <v>-0.000122964833281003</v>
+        <v>-0.000112542535394563</v>
       </c>
       <c r="D11">
-        <v>-2.32287815638951e-05</v>
+        <v>-1.28064836774551e-05</v>
       </c>
       <c r="E11">
-        <v>0.000158820833478655</v>
+        <v>0.000148398535592215</v>
       </c>
       <c r="F11">
-        <v>0.000122964833281003</v>
+        <v>0.000112542535394563</v>
       </c>
       <c r="G11">
         <v>9.97360517171078e-05</v>
@@ -428,7 +428,7 @@
         <v>3.58560001976522e-05</v>
       </c>
       <c r="I11">
-        <v>2.32287815638951e-05</v>
+        <v>1.28064836774551e-05</v>
       </c>
       <c r="J11">
         <v>-9.97360517171078e-05</v>
@@ -444,19 +444,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>2.34660800835089e-11</v>
+        <v>7.75285502113051e-08</v>
       </c>
       <c r="C12">
-        <v>-0.000116989939540092</v>
+        <v>-9.0184879289674e-05</v>
       </c>
       <c r="D12">
-        <v>-2.42165156773158e-05</v>
+        <v>2.58854457310261e-06</v>
       </c>
       <c r="E12">
-        <v>0.000140735081263951</v>
+        <v>0.000113930021013532</v>
       </c>
       <c r="F12">
-        <v>0.000116989939540092</v>
+        <v>9.0184879289674e-05</v>
       </c>
       <c r="G12">
         <v>9.27734238627766e-05</v>
@@ -465,7 +465,7 @@
         <v>2.37451417238585e-05</v>
       </c>
       <c r="I12">
-        <v>2.42165156773158e-05</v>
+        <v>-2.58854457310261e-06</v>
       </c>
       <c r="J12">
         <v>-9.27734238627766e-05</v>
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.26387326723506e-06</v>
+        <v>2.67347631285649e-06</v>
       </c>
       <c r="C13">
-        <v>-0.00253771386944988</v>
+        <v>-0.00216830131103052</v>
       </c>
       <c r="D13">
-        <v>-0.0037731443132673</v>
+        <v>-0.00340373175484794</v>
       </c>
       <c r="E13">
-        <v>0.00536676815577916</v>
+        <v>0.00499735559735979</v>
       </c>
       <c r="F13">
-        <v>0.00253771386944988</v>
+        <v>0.00216830131103052</v>
       </c>
       <c r="G13">
         <v>-0.00123543044381742</v>
@@ -502,7 +502,7 @@
         <v>0.00282905428632928</v>
       </c>
       <c r="I13">
-        <v>0.0037731443132673</v>
+        <v>0.00340373175484794</v>
       </c>
       <c r="J13">
         <v>0.00123543044381742</v>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>2.75896980321785e-13</v>
+        <v>7.39021167569003e-14</v>
       </c>
       <c r="C14">
-        <v>-0.00410058587918424</v>
+        <v>-0.00325345060783937</v>
       </c>
       <c r="D14">
-        <v>0.00425979069301057</v>
+        <v>0.00510692596435544</v>
       </c>
       <c r="E14">
-        <v>0.00767711230686733</v>
+        <v>0.00682997703552246</v>
       </c>
       <c r="F14">
-        <v>0.00410058587918424</v>
+        <v>0.00325345060783937</v>
       </c>
       <c r="G14">
         <v>0.00836037657219481</v>
@@ -539,7 +539,7 @@
         <v>0.00357652642768309</v>
       </c>
       <c r="I14">
-        <v>-0.00425979069301057</v>
+        <v>-0.00510692596435544</v>
       </c>
       <c r="J14">
         <v>-0.00836037657219481</v>
@@ -555,19 +555,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>1.36667007950072e-09</v>
+        <v>9.82868248582468e-11</v>
       </c>
       <c r="C15">
-        <v>-0.00902461684381705</v>
+        <v>-0.0103405171014726</v>
       </c>
       <c r="D15">
-        <v>-0.0138511657714844</v>
+        <v>-0.0151670660291399</v>
       </c>
       <c r="E15">
-        <v>0.0151261942727225</v>
+        <v>0.0164420945303781</v>
       </c>
       <c r="F15">
-        <v>0.00902461684381705</v>
+        <v>0.0103405171014726</v>
       </c>
       <c r="G15">
         <v>-0.00482654892766732</v>
@@ -576,7 +576,7 @@
         <v>0.00610157742890546</v>
       </c>
       <c r="I15">
-        <v>0.0138511657714844</v>
+        <v>0.0151670660291399</v>
       </c>
       <c r="J15">
         <v>0.00482654892766732</v>
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>2.52393284925888e-11</v>
+        <v>5.80511901622443e-10</v>
       </c>
       <c r="C16">
-        <v>-0.000742195660028042</v>
+        <v>-0.00077407563003362</v>
       </c>
       <c r="D16">
-        <v>-0.000790936606270928</v>
+        <v>-0.000822816576276506</v>
       </c>
       <c r="E16">
-        <v>0.00140026637486049</v>
+        <v>0.00143214634486607</v>
       </c>
       <c r="F16">
-        <v>0.000742195660028042</v>
+        <v>0.00077407563003362</v>
       </c>
       <c r="G16">
         <v>-4.87409462428857e-05</v>
@@ -613,7 +613,7 @@
         <v>0.00065807071483245</v>
       </c>
       <c r="I16">
-        <v>0.000790936606270928</v>
+        <v>0.000822816576276506</v>
       </c>
       <c r="J16">
         <v>4.87409462428857e-05</v>
@@ -629,19 +629,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.0853522007367718</v>
+        <v>0.0776520640526572</v>
       </c>
       <c r="C17">
-        <v>-3.49824040313249e-05</v>
+        <v>-3.32453543835851e-05</v>
       </c>
       <c r="D17">
-        <v>-4.2234148297988e-06</v>
+        <v>-2.48636518205897e-06</v>
       </c>
       <c r="E17">
-        <v>0.000264031546456473</v>
+        <v>0.000262294496808733</v>
       </c>
       <c r="F17">
-        <v>3.49824040313249e-05</v>
+        <v>3.32453543835851e-05</v>
       </c>
       <c r="G17">
         <v>3.07589892015261e-05</v>
@@ -650,7 +650,7 @@
         <v>0.000229049142425148</v>
       </c>
       <c r="I17">
-        <v>4.2234148297988e-06</v>
+        <v>2.48636518205897e-06</v>
       </c>
       <c r="J17">
         <v>-3.07589892015261e-05</v>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>4.92037927491457e-13</v>
+        <v>4.49669978482768e-10</v>
       </c>
       <c r="C18">
-        <v>-0.00225455412666114</v>
+        <v>-0.00211896207474638</v>
       </c>
       <c r="D18">
-        <v>-0.00163388252258301</v>
+        <v>-0.00149829047066825</v>
       </c>
       <c r="E18">
-        <v>0.00312801769801549</v>
+        <v>0.00299242564610073</v>
       </c>
       <c r="F18">
-        <v>0.00225455412666114</v>
+        <v>0.00211896207474638</v>
       </c>
       <c r="G18">
         <v>0.00062067160407813</v>
@@ -687,7 +687,7 @@
         <v>0.000873463571354348</v>
       </c>
       <c r="I18">
-        <v>0.00163388252258301</v>
+        <v>0.00149829047066825</v>
       </c>
       <c r="J18">
         <v>-0.00062067160407813</v>
@@ -703,19 +703,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>5.67049798405038e-10</v>
+        <v>4.87225573759075e-10</v>
       </c>
       <c r="C19">
-        <v>0.000702181135108861</v>
+        <v>0.000720471246105652</v>
       </c>
       <c r="D19">
-        <v>0.00140707833426339</v>
+        <v>0.00142536844526018</v>
       </c>
       <c r="E19">
-        <v>0.000174624579293387</v>
+        <v>0.000156334468296596</v>
       </c>
       <c r="F19">
-        <v>-0.000702181135108861</v>
+        <v>-0.000720471246105652</v>
       </c>
       <c r="G19">
         <v>0.000704897199154532</v>
@@ -724,7 +724,7 @@
         <v>0.000876805714402248</v>
       </c>
       <c r="I19">
-        <v>-0.00140707833426339</v>
+        <v>-0.00142536844526018</v>
       </c>
       <c r="J19">
         <v>-0.000704897199154532</v>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>9.95485484357194e-10</v>
+        <v>1.21094024236371e-09</v>
       </c>
       <c r="C20">
-        <v>0.000578148872071844</v>
+        <v>0.000576548061612162</v>
       </c>
       <c r="D20">
-        <v>0.000908476965767995</v>
+        <v>0.000906876155308314</v>
       </c>
       <c r="E20">
-        <v>0.000171763556344168</v>
+        <v>0.00017336436680385</v>
       </c>
       <c r="F20">
-        <v>-0.000578148872071844</v>
+        <v>-0.000576548061612162</v>
       </c>
       <c r="G20">
         <v>0.000330328093696152</v>
@@ -761,7 +761,7 @@
         <v>0.000749912428416012</v>
       </c>
       <c r="I20">
-        <v>-0.000908476965767995</v>
+        <v>-0.000906876155308314</v>
       </c>
       <c r="J20">
         <v>-0.000330328093696152</v>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>2.56135962415844e-08</v>
+        <v>1.99042877173713e-08</v>
       </c>
       <c r="C21">
-        <v>0.000508600515916312</v>
+        <v>0.000524268022542986</v>
       </c>
       <c r="D21">
-        <v>0.000760555267333984</v>
+        <v>0.000776222773960658</v>
       </c>
       <c r="E21">
-        <v>0.000195401055472238</v>
+        <v>0.000179733548845564</v>
       </c>
       <c r="F21">
-        <v>-0.000508600515916312</v>
+        <v>-0.000524268022542986</v>
       </c>
       <c r="G21">
         <v>0.000251954751417673</v>
@@ -798,7 +798,7 @@
         <v>0.000704001571388549</v>
       </c>
       <c r="I21">
-        <v>-0.000760555267333984</v>
+        <v>-0.000776222773960658</v>
       </c>
       <c r="J21">
         <v>-0.000251954751417673</v>
@@ -814,19 +814,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>7.22424468178975e-11</v>
+        <v>1.77554007762623e-12</v>
       </c>
       <c r="C22">
-        <v>-0.00893348705670048</v>
+        <v>-0.00891839856662305</v>
       </c>
       <c r="D22">
-        <v>-0.00919672421046665</v>
+        <v>-0.00918163572038923</v>
       </c>
       <c r="E22">
-        <v>0.00989137377057756</v>
+        <v>0.00987628528050014</v>
       </c>
       <c r="F22">
-        <v>0.00893348705670048</v>
+        <v>0.00891839856662305</v>
       </c>
       <c r="G22">
         <v>-0.000263237153766178</v>
@@ -835,7 +835,7 @@
         <v>0.000957886713877087</v>
       </c>
       <c r="I22">
-        <v>0.00919672421046665</v>
+        <v>0.00918163572038923</v>
       </c>
       <c r="J22">
         <v>0.000263237153766178</v>
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>7.55942930251676e-09</v>
+        <v>1.29501754611414e-10</v>
       </c>
       <c r="C23">
-        <v>-0.0104101048262757</v>
+        <v>-0.00918310063882797</v>
       </c>
       <c r="D23">
-        <v>-0.0083744866507394</v>
+        <v>-0.00714748246329171</v>
       </c>
       <c r="E23">
-        <v>0.0107251235416957</v>
+        <v>0.00949811935424804</v>
       </c>
       <c r="F23">
-        <v>0.0104101048262757</v>
+        <v>0.00918310063882797</v>
       </c>
       <c r="G23">
         <v>0.00203561817553626</v>
@@ -872,7 +872,7 @@
         <v>0.000315018715420073</v>
       </c>
       <c r="I23">
-        <v>0.0083744866507394</v>
+        <v>0.00714748246329171</v>
       </c>
       <c r="J23">
         <v>-0.00203561817553626</v>
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>4.55455208219234e-08</v>
+        <v>6.05140746547322e-10</v>
       </c>
       <c r="C24">
-        <v>-0.0144296376129205</v>
+        <v>-0.00329579650705065</v>
       </c>
       <c r="D24">
-        <v>-0.015937294278826</v>
+        <v>-0.00480345317295619</v>
       </c>
       <c r="E24">
-        <v>0.0167181491851807</v>
+        <v>0.00558430807931082</v>
       </c>
       <c r="F24">
-        <v>0.0144296376129205</v>
+        <v>0.00329579650705065</v>
       </c>
       <c r="G24">
         <v>-0.00150765666590554</v>
@@ -909,7 +909,7 @@
         <v>0.00228851157226018</v>
       </c>
       <c r="I24">
-        <v>0.015937294278826</v>
+        <v>0.00480345317295619</v>
       </c>
       <c r="J24">
         <v>0.00150765666590554</v>
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>7.51415478459592e-07</v>
+        <v>0.000103773373592129</v>
       </c>
       <c r="C25">
-        <v>-0.000510852686212662</v>
+        <v>-0.000359252529701084</v>
       </c>
       <c r="D25">
-        <v>0.00189004625592913</v>
+        <v>0.00204164641244071</v>
       </c>
       <c r="E25">
-        <v>0.00153405325753348</v>
+        <v>0.0013824531010219</v>
       </c>
       <c r="F25">
-        <v>0.000510852686212662</v>
+        <v>0.000359252529701084</v>
       </c>
       <c r="G25">
         <v>0.00240089894214179</v>
@@ -946,7 +946,7 @@
         <v>0.00102320057132082</v>
       </c>
       <c r="I25">
-        <v>-0.00189004625592913</v>
+        <v>-0.00204164641244071</v>
       </c>
       <c r="J25">
         <v>-0.00240089894214179</v>
@@ -962,19 +962,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>3.92800461075416e-13</v>
+        <v>3.23315904103329e-11</v>
       </c>
       <c r="C26">
-        <v>-0.00786460833062717</v>
+        <v>-0.00723548981997218</v>
       </c>
       <c r="D26">
-        <v>-0.00734179360525949</v>
+        <v>-0.00671267509460449</v>
       </c>
       <c r="E26">
-        <v>0.00832418033054897</v>
+        <v>0.00769506181989397</v>
       </c>
       <c r="F26">
-        <v>0.00786460833062717</v>
+        <v>0.00723548981997218</v>
       </c>
       <c r="G26">
         <v>0.000522814725367685</v>
@@ -983,7 +983,7 @@
         <v>0.000459571999921796</v>
       </c>
       <c r="I26">
-        <v>0.00734179360525949</v>
+        <v>0.00671267509460449</v>
       </c>
       <c r="J26">
         <v>-0.000522814725367685</v>
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>2.13110974206695e-08</v>
+        <v>3.64775560083422e-09</v>
       </c>
       <c r="C27">
-        <v>-0.0131102746864989</v>
+        <v>-0.0129545873543456</v>
       </c>
       <c r="D27">
-        <v>-0.011493274143764</v>
+        <v>-0.0113375868116106</v>
       </c>
       <c r="E27">
-        <v>0.0157654285430908</v>
+        <v>0.0156097412109375</v>
       </c>
       <c r="F27">
-        <v>0.0131102746864989</v>
+        <v>0.0129545873543456</v>
       </c>
       <c r="G27">
         <v>0.00161700054273492</v>
@@ -1020,7 +1020,7 @@
         <v>0.00265515385659195</v>
       </c>
       <c r="I27">
-        <v>0.011493274143764</v>
+        <v>0.0113375868116106</v>
       </c>
       <c r="J27">
         <v>-0.00161700054273492</v>
@@ -1036,19 +1036,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.00088769315453808</v>
+        <v>0.000984946476437904</v>
       </c>
       <c r="C28">
-        <v>0.000301080642592361</v>
+        <v>0.000289125653840269</v>
       </c>
       <c r="D28">
-        <v>3.1607491629464e-05</v>
+        <v>1.96525028773712e-05</v>
       </c>
       <c r="E28">
-        <v>0.000596727643694196</v>
+        <v>0.000608682632446289</v>
       </c>
       <c r="F28">
-        <v>-0.000301080642592361</v>
+        <v>-0.000289125653840269</v>
       </c>
       <c r="G28">
         <v>-0.000269473150962897</v>
@@ -1057,7 +1057,7 @@
         <v>0.000897808286286558</v>
       </c>
       <c r="I28">
-        <v>-3.1607491629464e-05</v>
+        <v>-1.96525028773712e-05</v>
       </c>
       <c r="J28">
         <v>0.000269473150962897</v>
@@ -1073,19 +1073,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>4.90886128769323e-07</v>
+        <v>2.52062632317975e-06</v>
       </c>
       <c r="C29">
-        <v>-0.0130527588901584</v>
+        <v>-0.0109492939461364</v>
       </c>
       <c r="D29">
-        <v>-0.0114854744502477</v>
+        <v>-0.00938200950622559</v>
       </c>
       <c r="E29">
-        <v>0.0178271361759731</v>
+        <v>0.015723671231951</v>
       </c>
       <c r="F29">
-        <v>0.0130527588901584</v>
+        <v>0.0109492939461364</v>
       </c>
       <c r="G29">
         <v>0.00156728443991077</v>
@@ -1094,7 +1094,7 @@
         <v>0.00477437728581468</v>
       </c>
       <c r="I29">
-        <v>0.0114854744502477</v>
+        <v>0.00938200950622559</v>
       </c>
       <c r="J29">
         <v>-0.00156728443991077</v>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>9.68699773368917e-19</v>
+        <v>2.50671252859819e-20</v>
       </c>
       <c r="C30">
-        <v>0.0239285544090048</v>
+        <v>0.0252863822767852</v>
       </c>
       <c r="D30">
-        <v>-0.0103307792118617</v>
+        <v>-0.00897295134408134</v>
       </c>
       <c r="E30">
-        <v>0.0123712675912039</v>
+        <v>0.0110134397234236</v>
       </c>
       <c r="F30">
-        <v>-0.0239285544090048</v>
+        <v>-0.0252863822767852</v>
       </c>
       <c r="G30">
         <v>-0.0342593336208665</v>
@@ -1131,7 +1131,7 @@
         <v>0.0362998220002087</v>
       </c>
       <c r="I30">
-        <v>0.0103307792118617</v>
+        <v>0.00897295134408134</v>
       </c>
       <c r="J30">
         <v>0.0342593336208665</v>
@@ -1147,19 +1147,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.00608343833347923</v>
+        <v>0.00326131055360953</v>
       </c>
       <c r="C31">
-        <v>-0.00177798140430241</v>
+        <v>-0.00199170663056848</v>
       </c>
       <c r="D31">
-        <v>-0.00402797971452986</v>
+        <v>-0.00424170494079592</v>
       </c>
       <c r="E31">
-        <v>0.0114174229758126</v>
+        <v>0.0116311482020787</v>
       </c>
       <c r="F31">
-        <v>0.00177798140430241</v>
+        <v>0.00199170663056848</v>
       </c>
       <c r="G31">
         <v>-0.00224999831022744</v>
@@ -1168,7 +1168,7 @@
         <v>0.00963944157151023</v>
       </c>
       <c r="I31">
-        <v>0.00402797971452986</v>
+        <v>0.00424170494079592</v>
       </c>
       <c r="J31">
         <v>0.00224999831022744</v>
@@ -1184,19 +1184,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>5.30745885736111e-14</v>
+        <v>3.63880790461969e-06</v>
       </c>
       <c r="C32">
-        <v>-0.00465238494091734</v>
+        <v>-0.00339435227838944</v>
       </c>
       <c r="D32">
-        <v>-0.00317396436418806</v>
+        <v>-0.00191593170166016</v>
       </c>
       <c r="E32">
-        <v>0.0070927483694894</v>
+        <v>0.0058347157069615</v>
       </c>
       <c r="F32">
-        <v>0.00465238494091734</v>
+        <v>0.00339435227838944</v>
       </c>
       <c r="G32">
         <v>0.00147842057672928</v>
@@ -1205,7 +1205,7 @@
         <v>0.00244036342857206</v>
       </c>
       <c r="I32">
-        <v>0.00317396436418806</v>
+        <v>0.00191593170166016</v>
       </c>
       <c r="J32">
         <v>-0.00147842057672928</v>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>5.81972028258988e-07</v>
+        <v>5.66107226528233e-08</v>
       </c>
       <c r="C33">
-        <v>-0.00176859622713112</v>
+        <v>-0.00202227359529518</v>
       </c>
       <c r="D33">
-        <v>-0.00225789206368583</v>
+        <v>-0.00251156943184989</v>
       </c>
       <c r="E33">
-        <v>0.0040191582271031</v>
+        <v>0.00427283559526716</v>
       </c>
       <c r="F33">
-        <v>0.00176859622713112</v>
+        <v>0.00202227359529518</v>
       </c>
       <c r="G33">
         <v>-0.000489295836554707</v>
@@ -1242,7 +1242,7 @@
         <v>0.00225056199997198</v>
       </c>
       <c r="I33">
-        <v>0.00225789206368583</v>
+        <v>0.00251156943184989</v>
       </c>
       <c r="J33">
         <v>0.000489295836554707</v>
